--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B72FEE-E12C-43CF-A0F8-F6DE4EFCE494}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8746B884-0594-4210-A202-6DB22E35169E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -606,18 +606,6 @@
 💡 포기서 양식 등은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
   </si>
   <si>
-    <t>📚 마이크로디그리(소단위전공과정)란?
-적은 학점으로 다양한 전공을 경험해 볼 수 있는 제도입니다.
-📊 특징:
-▸ 과정별 8~12학점 이수
-▸ 본인 전공과목과 중복 인정 가능
-▸ 3개 교과목 이상 이수 시 연계전공 신청 가능
-▸ 이수건수 제한 없음
-▸ 이수 시 별도의 이수증 발급
-📋 37개의 과정이 있음 (식품품질관리 MD, 반려동물 MD 등)
-💡 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!</t>
-  </si>
-  <si>
     <t>💰 등록금 안내
 ▸ 원전공 기준의 등록금을 납부하면 됨
 ▸ 다전공을 신청해도 추가 등록금 없음!
@@ -1067,341 +1055,6 @@
         <rFont val="Segoe UI Emoji"/>
         <family val="2"/>
       </rPr>
-      <t>📚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 마이크로디그리(소단위전공과정)란?
-적은 학점으로 다양한 전공을 경험해 볼 수 있는 제도입니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 특징:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 과정별 8~12학점 이수
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 3개 교과목 이상 이수 시 연계전공 신청 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 이수건수 제한 없음
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 이수 시 별도의 이수증 발급
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 37개의 과정이 있음 (식품품질관리 MD, 반려동물 MD 등)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자세한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사항은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>왼쪽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이드바의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>다전공</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>안내' 참고</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
       <t>📊</t>
     </r>
     <r>
@@ -13775,6 +13428,533 @@
   </si>
   <si>
     <t>유연학사제도가뭐, 유연학사제도뭐, 유연학사제도에대해설명, 유연학사제도가무엇, 유연학사제도개념, 유연학사제도의개념, 유연학사제도의정의, 유연학사제도정의, 유연학사제도알려, 유연학사제도에대해알려, 유연학사제도설명, 유연학사제도는뭐, 유연학사제도, 유연학사제도무엇, 유연학사제도의개념, 유연학사제도의정의, 유연학사제도정의, 유연학사제도개념, 유연학사제도정보알려, 유연학사제도가뭔지, 유연학사제도뭔지, 유연학사제도의의미, 유연학사제도의미, 유연학사제도내용, 유연학사제도상세, 유연학사제도자세히, 유연하가제도구체적으로, 유연학사제도는어떤제도, 유연학사제도는어떤전공, 유연학사제도에는어떤전공, 유연학사제도는무슨전공, 유연학사제도무슨전공, 유연학사제도궁금, 유연학사제도에대해알고싶, 유연학사제도를알고싶, 유연학사제도모르겠, 유연학사가뭐, 유연학사뭐, 유연학사는뭐, 유연학사제도는뭔데, 유연학사제도가뭔데, 유연학사제도가뭘, 유연학사제도뭔데, 유연학사가뭐, 유연학사뭐, 유연학사에대해설명, 유연학사알려, 유연학사설명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 마이크로디그리(소단위전공과정)란?
+적은 학점으로 다양한 전공을 경험해 볼 수 있는 제도입니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 특징:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 과정별 8~12학점 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 3개 교과목 이상 이수 시 연계전공 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수건수 제한 없음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수 시 별도의 이수증 발급
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 55개의 과정이 있음 (식품품질관리 MD, 반려동물 MD 등)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자세한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사항은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왼쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이드바의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>안내' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 마이크로디그리(소단위전공과정)란?
+적은 학점으로 다양한 전공을 경험해 볼 수 있는 제도입니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 특징:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 과정별 8~12학점 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 3개 교과목 이상 이수 시 연계전공 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수건수 제한 없음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수 시 별도의 이수증 발급
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 55개의 과정이 있음 (식품품질관리 MD, 반려동물 MD 등)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -14314,7 +14494,7 @@
         <v>168</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -14448,7 +14628,7 @@
         <v>111</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -14465,7 +14645,7 @@
         <v>112</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -14482,7 +14662,7 @@
         <v>113</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -14499,7 +14679,7 @@
         <v>114</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -14516,7 +14696,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -14533,7 +14713,7 @@
         <v>116</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -14553,7 +14733,7 @@
         <v>169</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -14573,7 +14753,7 @@
         <v>169</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -14874,7 +15054,7 @@
         <v>135</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -14891,7 +15071,7 @@
         <v>136</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -14908,7 +15088,7 @@
         <v>137</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -14928,7 +15108,7 @@
         <v>99</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -14948,7 +15128,7 @@
         <v>98</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -14965,7 +15145,7 @@
         <v>140</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -14985,7 +15165,7 @@
         <v>169</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -14999,13 +15179,13 @@
         <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E41" t="s">
         <v>169</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -15016,13 +15196,13 @@
         <v>84</v>
       </c>
       <c r="C42" t="s">
+        <v>229</v>
+      </c>
+      <c r="D42" t="s">
+        <v>232</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="D42" t="s">
-        <v>234</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -15036,10 +15216,10 @@
         <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -15053,10 +15233,10 @@
         <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -15070,10 +15250,10 @@
         <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -15087,10 +15267,10 @@
         <v>98</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -15104,10 +15284,10 @@
         <v>99</v>
       </c>
       <c r="D47" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -15121,10 +15301,10 @@
         <v>100</v>
       </c>
       <c r="D48" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -15138,13 +15318,13 @@
         <v>102</v>
       </c>
       <c r="D49" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E49" t="s">
         <v>169</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -15161,7 +15341,7 @@
         <v>142</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -15178,7 +15358,7 @@
         <v>143</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -15195,7 +15375,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -15212,7 +15392,7 @@
         <v>145</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -15229,7 +15409,7 @@
         <v>146</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -15246,7 +15426,7 @@
         <v>147</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -15266,7 +15446,7 @@
         <v>169</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -15286,7 +15466,7 @@
         <v>169</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -15303,7 +15483,7 @@
         <v>150</v>
       </c>
       <c r="F58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -15320,7 +15500,7 @@
         <v>151</v>
       </c>
       <c r="F59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -15337,7 +15517,7 @@
         <v>152</v>
       </c>
       <c r="F60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -15354,7 +15534,7 @@
         <v>153</v>
       </c>
       <c r="F61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -15371,7 +15551,7 @@
         <v>154</v>
       </c>
       <c r="F62" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -15388,7 +15568,7 @@
         <v>155</v>
       </c>
       <c r="F63" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -15405,7 +15585,7 @@
         <v>156</v>
       </c>
       <c r="F64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -15425,7 +15605,7 @@
         <v>169</v>
       </c>
       <c r="F65" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -15444,8 +15624,8 @@
       <c r="E66" t="s">
         <v>169</v>
       </c>
-      <c r="F66" t="s">
-        <v>179</v>
+      <c r="F66" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -15462,7 +15642,7 @@
         <v>159</v>
       </c>
       <c r="F67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -15479,7 +15659,7 @@
         <v>160</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -15496,7 +15676,7 @@
         <v>161</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -15513,7 +15693,7 @@
         <v>162</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -15530,7 +15710,7 @@
         <v>163</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -15547,7 +15727,7 @@
         <v>164</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -15564,7 +15744,7 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -15581,12 +15761,12 @@
         <v>166</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B75" t="s">
         <v>94</v>
@@ -15598,7 +15778,7 @@
         <v>167</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8746B884-0594-4210-A202-6DB22E35169E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8088E48-EEEB-4CBA-9449-99B0286C210E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$75</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -654,18 +657,6 @@
 📞 학사지원팀: 031-670-5036</t>
   </si>
   <si>
-    <t>📚 소단위전공과정(마이크로디그리)란?
-적은 학점으로 다양한 전공을 경험해 볼 수 있는 제도입니다.
-📊 특징:
-▸ 과정별 8~12학점 이수
-▸ 본인 전공과목과 중복 인정 가능
-▸ 3개 교과목 이상 이수 시 연계전공 신청 가능
-▸ 이수건수 제한 없음
-▸ 이수 시 별도의 이수증 발급
-📋 37개의 과정이 있음 (식품품질관리 MD, 반려동물 MD 등)
-💡 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!</t>
-  </si>
-  <si>
     <t>📊 성적/수강 확인 안내
 성적확인, 이수학점 확인, 수강조회 등
 💻 학사시스템에서 확인: https://info.hknu.ac.kr</t>
@@ -7569,707 +7560,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 소단위전공과정(마이크로디그리) 특징
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 과정별 8~12학점만 이수
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 3개 교과목 이상 이수 시 연계전공 신청 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 이수건수 제한 없음
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>⚠️</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 복수전공, 부전공, 융합전공, 융합부전공, 연계전공 중 1개만 참여 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 마이크로디그리는 제한 없이 여러 개 이수 가능!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자세한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사항은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>왼쪽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이드바의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>다전공</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>참고</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 마이크로디그리(소단위전공과정) 특징
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 과정별 8~12학점만 이수
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 3개 교과목 이상 이수 시 연계전공 신청 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 이수건수 제한 없음
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>⚠️</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 복수전공, 부전공, 융합전공, 융합부전공, 연계전공 중 1개만 참여 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 마이크로디그리는 제한 없이 여러 개 이수 가능!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자세한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사항은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>왼쪽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이드바의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>다전공</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">'  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>참고</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> 다전공별 이수학점 안내
 </t>
     </r>
@@ -13438,6 +12728,707 @@
         <rFont val="Segoe UI Emoji"/>
         <family val="2"/>
       </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 소단위전공과정(마이크로디그리) 특징
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 과정별 8~12학점만 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수건수 제한 없음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 복수전공, 부전공, 융합전공, 융합부전공, 연계전공 중 1개만 참여 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 마이크로디그리는 제한 없이 여러 개 이수 가능!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자세한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사항은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왼쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이드바의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 마이크로디그리(소단위전공과정) 특징
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 과정별 8~12학점만 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수건수 제한 없음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 복수전공, 부전공, 융합전공, 융합부전공, 연계전공 중 1개만 참여 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 마이크로디그리는 제한 없이 여러 개 이수 가능!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자세한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사항은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왼쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이드바의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">'  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
       <t>📚</t>
     </r>
     <r>
@@ -13534,7 +13525,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 3개 교과목 이상 이수 시 연계전공 신청 가능
+      <t xml:space="preserve"> 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
 </t>
     </r>
     <r>
@@ -13762,6 +13753,198 @@
         <scheme val="minor"/>
       </rPr>
       <t>안내' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 소단위전공과정(마이크로디그리)란?
+적은 학점으로 다양한 전공을 경험해 볼 수 있는 제도입니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 특징:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 과정별 8~12학점 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수건수 제한 없음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수 시 별도의 이수증 발급
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 55개의 과정이 있음 (식품품질관리 MD, 반려동물 MD 등)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -13869,7 +14052,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 3개 교과목 이상 이수 시 연계전공 신청 가능
+      <t xml:space="preserve"> 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
 </t>
     </r>
     <r>
@@ -14494,7 +14677,7 @@
         <v>168</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -14628,7 +14811,7 @@
         <v>111</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -14645,7 +14828,7 @@
         <v>112</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -14662,7 +14845,7 @@
         <v>113</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -14679,7 +14862,7 @@
         <v>114</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -14696,7 +14879,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -14713,7 +14896,7 @@
         <v>116</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -14733,7 +14916,7 @@
         <v>169</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -14753,7 +14936,7 @@
         <v>169</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -15054,7 +15237,7 @@
         <v>135</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -15071,7 +15254,7 @@
         <v>136</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -15088,7 +15271,7 @@
         <v>137</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -15108,7 +15291,7 @@
         <v>99</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -15128,7 +15311,7 @@
         <v>98</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -15145,7 +15328,7 @@
         <v>140</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -15165,7 +15348,7 @@
         <v>169</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -15179,13 +15362,13 @@
         <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E41" t="s">
         <v>169</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -15196,13 +15379,13 @@
         <v>84</v>
       </c>
       <c r="C42" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" t="s">
         <v>229</v>
       </c>
-      <c r="D42" t="s">
-        <v>232</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -15216,10 +15399,10 @@
         <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -15233,10 +15416,10 @@
         <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -15250,10 +15433,10 @@
         <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -15267,10 +15450,10 @@
         <v>98</v>
       </c>
       <c r="D46" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -15284,10 +15467,10 @@
         <v>99</v>
       </c>
       <c r="D47" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -15301,10 +15484,10 @@
         <v>100</v>
       </c>
       <c r="D48" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -15318,13 +15501,13 @@
         <v>102</v>
       </c>
       <c r="D49" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E49" t="s">
         <v>169</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -15341,7 +15524,7 @@
         <v>142</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -15358,7 +15541,7 @@
         <v>143</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -15375,7 +15558,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -15392,7 +15575,7 @@
         <v>145</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -15409,7 +15592,7 @@
         <v>146</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -15426,7 +15609,7 @@
         <v>147</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -15446,7 +15629,7 @@
         <v>169</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -15466,7 +15649,7 @@
         <v>169</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -15604,8 +15787,8 @@
       <c r="E65" t="s">
         <v>169</v>
       </c>
-      <c r="F65" t="s">
-        <v>186</v>
+      <c r="F65" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -15642,7 +15825,7 @@
         <v>159</v>
       </c>
       <c r="F67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -15659,7 +15842,7 @@
         <v>160</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -15676,7 +15859,7 @@
         <v>161</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -15693,7 +15876,7 @@
         <v>162</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -15710,7 +15893,7 @@
         <v>163</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -15727,7 +15910,7 @@
         <v>164</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -15744,7 +15927,7 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -15761,12 +15944,12 @@
         <v>166</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B75" t="s">
         <v>94</v>
@@ -15778,7 +15961,7 @@
         <v>167</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8088E48-EEEB-4CBA-9449-99B0286C210E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E76C97A-34B2-4E53-A70E-42FDF20F2FBE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="236">
   <si>
     <t>faq_id</t>
   </si>
@@ -11722,549 +11722,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 신청 자격: 입학 후 첫 학기부터 신청 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자세한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사항은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>학사공지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>참조</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>또는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>왼쪽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이드바의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>다전공</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>참고</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 신청 자격: 입학 후 첫 학기부터 신청 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 단, 신입생은 2020학번 이후부터, 편입생은 2022학번 이후부터 신청 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>자세한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사항은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>학사공지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>참조</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>또는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>왼쪽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사이드바의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>다전공</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>제도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>참고</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>F074</t>
   </si>
   <si>
@@ -14137,6 +13594,850 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 자격: 입학 후 첫 학기부터 재학생이면 누구나 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자세한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사항은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>학사공지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>또는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왼쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이드바의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 자격: 입학 후 첫 학기부터 재학생이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">누구나 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 단, 신입생은 2020학번 이후부터, 편입생은 2022학번 이후부터 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자세한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사항은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>학사공지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>또는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왼쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이드바의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 자격: 입학 후 첫 학기부터 재학생이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">누구나 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>자세한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사항은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>학사공지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>또는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왼쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이드바의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>참고</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -14618,6 +14919,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -14828,7 +15130,7 @@
         <v>112</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -14845,7 +15147,7 @@
         <v>113</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -14862,7 +15164,7 @@
         <v>114</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -14879,7 +15181,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -14896,7 +15198,7 @@
         <v>116</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -14916,7 +15218,7 @@
         <v>169</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -14936,7 +15238,7 @@
         <v>169</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -15348,7 +15650,7 @@
         <v>169</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -15368,7 +15670,7 @@
         <v>169</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -15379,13 +15681,13 @@
         <v>84</v>
       </c>
       <c r="C42" t="s">
+        <v>224</v>
+      </c>
+      <c r="D42" t="s">
+        <v>227</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="D42" t="s">
-        <v>229</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -15399,7 +15701,7 @@
         <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>201</v>
@@ -15507,7 +15809,7 @@
         <v>169</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -15788,7 +16090,7 @@
         <v>169</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -15808,7 +16110,7 @@
         <v>169</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -15949,7 +16251,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B75" t="s">
         <v>94</v>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -2122,7 +2122,13 @@
 ▸ 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
 ▸ 이수건수 제한 없음
 ▸ 이수 시 별도의 이수증 발급
-📋 55개의 과정이 있음 (식품품질관리 MD, 반려동물 MD 등)
+📋 마이크로디그리 과정 목록 (총 55개):
+▸ AI·반도체·IT (20개): 사물인터넷, 통신공학, AI보안, AI화학공학, 반도체 설계/공정/소재/부품장비, AIoT보안, 미래모빌리티, 첨단소재공학 등
+▸ 농생명·바이오·식품 (9개): 식품품질관리, 반려동물, 유전체 육종번식, 축산식품과 HACCP, 생명공학연구실습, 식물원학 등
+▸ 인문·사회·교육 (8개): 공공 PR, 정책분석평가, 의료수어통역, 청소년상담가과정, 유아 교과 수업설계 등
+▸ 디자인·문화·예술 (7개): 브랜드 콘텐츠, 내러티브 디자인, 컴퓨터음악, 3D 프린팅 디자이너, 귀금속보석공예 등
+▸ 에너지·환경·안전 (6개): 인프라 재난방재, 바이오에너지, 산업보건 및 위생, 탄소중립 전기에너지 등
+▸ 경영·재무·마케팅 (5개): 그로스마케터 과정, 재무빅데이터분석 전문가, 글로벌 비즈니스 등
 💡 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!
 💡 자세한 사항은 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
         </is>
@@ -2679,7 +2685,13 @@
 ▸ 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
 ▸ 이수건수 제한 없음
 ▸ 이수 시 별도의 이수증 발급
-📋 55개의 과정이 있음 (식품품질관리 MD, 반려동물 MD 등)
+📋 마이크로디그리 과정 목록 (총 55개):
+▸ AI·반도체·IT (20개): 사물인터넷, 통신공학, AI보안, AI화학공학, 반도체 설계/공정/소재/부품장비, AIoT보안, 미래모빌리티, 첨단소재공학 등
+▸ 농생명·바이오·식품 (9개): 식품품질관리, 반려동물, 유전체 육종번식, 축산식품과 HACCP, 생명공학연구실습, 식물원학 등
+▸ 인문·사회·교육 (8개): 공공 PR, 정책분석평가, 의료수어통역, 청소년상담가과정, 유아 교과 수업설계 등
+▸ 디자인·문화·예술 (7개): 브랜드 콘텐츠, 내러티브 디자인, 컴퓨터음악, 3D 프린팅 디자이너, 귀금속보석공예 등
+▸ 에너지·환경·안전 (6개): 인프라 재난방재, 바이오에너지, 산업보건 및 위생, 탄소중립 전기에너지 등
+▸ 경영·재무·마케팅 (5개): 그로스마케터 과정, 재무빅데이터분석 전문가, 글로벌 비즈니스 등
 💡 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!</t>
         </is>
       </c>
@@ -2720,7 +2732,13 @@
 ▸ 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
 ▸ 이수건수 제한 없음
 ▸ 이수 시 별도의 이수증 발급
-📋 55개의 과정이 있음 (식품품질관리 MD, 반려동물 MD 등)
+📋 마이크로디그리 과정 목록 (총 55개):
+▸ AI·반도체·IT (20개): 사물인터넷, 통신공학, AI보안, AI화학공학, 반도체 설계/공정/소재/부품장비, AIoT보안, 미래모빌리티, 첨단소재공학 등
+▸ 농생명·바이오·식품 (9개): 식품품질관리, 반려동물, 유전체 육종번식, 축산식품과 HACCP, 생명공학연구실습, 식물원학 등
+▸ 인문·사회·교육 (8개): 공공 PR, 정책분석평가, 의료수어통역, 청소년상담가과정, 유아 교과 수업설계 등
+▸ 디자인·문화·예술 (7개): 브랜드 콘텐츠, 내러티브 디자인, 컴퓨터음악, 3D 프린팅 디자이너, 귀금속보석공예 등
+▸ 에너지·환경·안전 (6개): 인프라 재난방재, 바이오에너지, 산업보건 및 위생, 탄소중립 전기에너지 등
+▸ 경영·재무·마케팅 (5개): 그로스마케터 과정, 재무빅데이터분석 전문가, 글로벌 비즈니스 등
 💡 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!</t>
         </is>
       </c>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3033,6 +3033,33 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PROGRAM_COMPARISON</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>마이크로디그리</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>마이크로디그리 소단위전공과정 똑같아,마이크로디그리 소단위전공과정 같은거,마이크로디그리 소단위전공과정 차이,소단위전공과정 마이크로디그리 뭐가달라,마이크로디그리 소단위 같은건가,마이크로디그리 소단위 다른거야</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>✅ 마이크로디그리와 소단위전공과정은 같은 제도입니다!
+📌 정식 명칭은 **소단위전공과정**이며, **마이크로디그리(Micro Degree, MD)**는 같은 제도의 줄임말/별칭입니다.
+💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는
+💡 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -2520,10 +2520,10 @@
 ▸ 재학증명서, 졸업증명서, 성적증명서, 수료증명서 등
 ▸ 국문/영문 모두 발급 가능
 💻 온라인 발급:
-▸ 학사시스템(https://info.hknu.ac.kr) 또는 정부24에서 발급 가능
-▸ 24시간 이용 가능 (일부 증명서 제외)
+▸ 정부24(https://www.gov.kr)에서 발급 가능
+▸ 써트피아(https://certpia.com)에서 발급 가능
 🏢 오프라인 발급:
-▸ 본관 1층 무인발급기 또는 학사지원팀 방문
+▸ 본관 1층 무인발급기 이용
 📌 전과(전공변경), 휴복학, 재입학 등도 학사지원팀에서 처리
 💡 학사공지 참조: https://www.hknu.ac.kr/kor/562/subview.do
 📞 학사지원팀: 031-670-5037</t>
@@ -2556,11 +2556,10 @@
         <is>
           <t>🔄 학점교류 안내
 📌 학점교류란?
-▸ 타 대학에서 이수한 학점을 본교 학점으로 인정받는 제도
+▸ 국내외 대학에서 이수한 학점을 본교 학점으로 인정받는 제도
 📋 종류:
-▸ 국내 대학 학점교류 (협약 대학 간)
+▸ 국내외 대학 학점교류 (협약 대학 간)
 ▸ 계절학기 (여름/겨울 방학 중 타교 수강)
-▸ 교환학생 프로그램
 📌 유의사항:
 ▸ 사전에 학점인정 신청 필요
 ▸ 이수구분(전필, 전선, 교양 등) 확인 후 신청
@@ -2602,8 +2601,8 @@
 ▸ 학기 중 수강철회 기간에 신청 가능
 ▸ 철회한 과목은 성적표에 'W'로 표기
 ▸ 재수강과 다름 (재수강은 이전 성적 대체)
-📌 성적 관련:
-▸ 성적 이의신청: 성적 공시 후 정정기간 내 신청
+📌 성적 이의신청:
+▸ 성적 공시 후 정정기간 내 신청
 ▸ 성적확인: 학사시스템(https://info.hknu.ac.kr)에서 조회
 💡 학사공지 참조: https://www.hknu.ac.kr/kor/562/subview.do
 📞 학사지원팀: 031-670-5032</t>
@@ -2637,12 +2636,11 @@
           <t>👨‍🏫 교직 이수 안내
 📌 교직과정이란?
 ▸ 소정의 교직과목을 이수하여 교원자격증(2급 정교사)을 취득하는 과정
-📋 이수 조건:
+📋 신청 자격:
 ▸ 교직과정 설치 학과 학생만 신청 가능
-▸ 2학년 진급 시 신청 (학과별 선발인원 제한)
+▸ 학과별 선발인원 제한 있음
+📌 이수 조건:
 ▸ 전공과목 + 교직과목 + 교육실습 이수 필요
-📌 자유학기제:
-▸ 자유학기제 관련 교직 이수도 가능
 📌 유의사항:
 ▸ 교직 적성·인성검사 통과 필요
 ▸ 응급처치 실습 이수 필요
@@ -2805,15 +2803,8 @@
       <c r="F67" t="inlineStr">
         <is>
           <t>📊 성적/수강 확인 안내
-💻 확인 방법:
-▸ 학사시스템 접속: https://info.hknu.ac.kr
-▸ 로그인 후 학적관리 메뉴에서 조회
-📌 확인 가능 항목:
-▸ 학기별 성적 조회
-▸ 전체 이수학점 확인
-▸ 수강신청 내역 확인
-▸ 평균평점(GPA) 확인
-💡 성적 이의신청은 성적 공시 후 정정기간 내 학사시스템에서 가능
+성적확인, 이수학점 확인, 수강조회 등
+💻 학사시스템에서 확인: https://info.hknu.ac.kr
 📞 학사지원팀: 031-670-5032</t>
         </is>
       </c>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -662,7 +662,11 @@
           <t>소단위전공과정</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>nan, 소단위전공과정신청기간</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>가능,되나,포기,취소</t>
@@ -726,7 +730,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>다전공자격, 다전공조건, 다전공가능, 다전공누가, 다전공몇학년, 다전공필요학점, 다전공평점, 다전공GPA, 다전공신청자격, 다전공지원자격, 다전공요건, 다전공신청할수있나, 다전공신청가능한가, 다전공신청할수있는, 다전공자격있나, 다전공자격되나, 다전공자격충족, 다전공학점요구, 다전공학점필요, 다전공최소학점, 다전공신청요건, 다전공신청조건은, 다전공필요한조건, 다전공제한사항, 다전공제약, 다전공불가능한경우, 다전공학년제한있나, 다전공평점필요, 다전공평점기준, 다전공누구나가능, 다전공모두가능</t>
+          <t>다전공자격, 다전공조건, 다전공가능, 다전공누가, 다전공몇학년, 다전공필요학점, 다전공평점, 다전공GPA, 다전공신청자격, 다전공지원자격, 다전공요건, 다전공신청할수있나, 다전공신청가능한가, 다전공신청할수있는, 다전공자격있나, 다전공자격되나, 다전공자격충족, 다전공학점요구, 다전공학점필요, 다전공최소학점, 다전공신청요건, 다전공신청조건은, 다전공필요한조건, 다전공제한사항, 다전공제약, 다전공불가능한경우, 다전공학년제한있나, 다전공평점필요, 다전공평점기준, 다전공누구나가능, 다전공모두가능, 다전공신청돼, 다전공돼, 다전공가능해, 다전공가능한가, 다전공할수있나, 다전공대상, 다전공1학년, 다전공편입생, 다전공편입</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -757,7 +761,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>복수전공자격, 복수전공조건, 복수전공가능, 복수전공누가, 복수전공몇학년, 복수전공필요학점, 복수전공평점, 복수전공GPA, 복수전공신청자격, 복수전공지원자격, 복수전공요건, 복수전공신청할수있나, 복수전공신청가능한가, 복수전공신청할수있는, 복수전공자격있나, 복수전공자격되나, 복수전공자격충족, 복수전공학점요구, 복수전공학점필요, 복수전공최소학점, 복수전공신청요건, 복수전공신청조건은, 복수전공필요한조건, 복수전공제한사항, 복수전공제약, 복수전공불가능한경우, 복수전공학년제한있나, 복수전공평점필요, 복수전공평점기준, 복수전공누구나가능, 복수전공모두가능</t>
+          <t>복수전공자격, 복수전공조건, 복수전공가능, 복수전공누가, 복수전공몇학년, 복수전공필요학점, 복수전공평점, 복수전공GPA, 복수전공신청자격, 복수전공지원자격, 복수전공요건, 복수전공신청할수있나, 복수전공신청가능한가, 복수전공신청할수있는, 복수전공자격있나, 복수전공자격되나, 복수전공자격충족, 복수전공학점요구, 복수전공학점필요, 복수전공최소학점, 복수전공신청요건, 복수전공신청조건은, 복수전공필요한조건, 복수전공제한사항, 복수전공제약, 복수전공불가능한경우, 복수전공학년제한있나, 복수전공평점필요, 복수전공평점기준, 복수전공누구나가능, 복수전공모두가능, 복수전공신청돼, 복수전공돼, 복수전공가능해, 복수전공가능한가, 복수전공할수있나, 복수전공대상, 복수전공1학년, 복수전공편입생, 복수전공편입</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -787,7 +791,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>부전공자격, 부전공조건, 부전공가능, 부전공누가, 부전공몇학년, 부전공필요학점, 부전공평점, 부전공GPA, 부전공신청자격, 부전공지원자격, 부전공요건, 부전공신청할수있나, 부전공신청가능한가, 부전공신청할수있는, 부전공자격있나, 부전공자격되나, 부전공자격충족, 부전공학점요구, 부전공학점필요, 부전공최소학점, 부전공신청요건, 부전공신청조건은, 부전공필요한조건, 부전공제한사항, 부전공제약, 부전공불가능한경우, 부전공학년제한있나, 부전공평점필요, 부전공평점기준, 부전공누구나가능, 부전공모두가능</t>
+          <t>부전공자격, 부전공조건, 부전공가능, 부전공누가, 부전공몇학년, 부전공필요학점, 부전공평점, 부전공GPA, 부전공신청자격, 부전공지원자격, 부전공요건, 부전공신청할수있나, 부전공신청가능한가, 부전공신청할수있는, 부전공자격있나, 부전공자격되나, 부전공자격충족, 부전공학점요구, 부전공학점필요, 부전공최소학점, 부전공신청요건, 부전공신청조건은, 부전공필요한조건, 부전공제한사항, 부전공제약, 부전공불가능한경우, 부전공학년제한있나, 부전공평점필요, 부전공평점기준, 부전공누구나가능, 부전공모두가능, 부전공신청돼, 부전공돼, 부전공가능해, 부전공가능한가, 부전공할수있나, 부전공대상, 부전공1학년, 부전공편입생, 부전공편입</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -818,7 +822,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>융합전공자격, 융합전공조건, 융합전공가능, 융합전공누가, 융합전공몇학년, 융합전공필요학점, 융합전공평점, 융합전공GPA, 융합전공신청자격, 융합전공지원자격, 융합전공요건, 융합전공신청할수있나, 융합전공신청가능한가, 융합전공신청할수있는, 융합전공자격있나, 융합전공자격되나, 융합전공자격충족, 융합전공학점요구, 융합전공학점필요, 융합전공최소학점, 융합전공신청요건, 융합전공신청조건은, 융합전공필요한조건, 융합전공제한사항, 융합전공제약, 융합전공불가능한경우, 융합전공학년제한있나, 융합전공평점필요, 융합전공평점기준, 융합전공누구나가능, 융합전공모두가능</t>
+          <t>융합전공자격, 융합전공조건, 융합전공가능, 융합전공누가, 융합전공몇학년, 융합전공필요학점, 융합전공평점, 융합전공GPA, 융합전공신청자격, 융합전공지원자격, 융합전공요건, 융합전공신청할수있나, 융합전공신청가능한가, 융합전공신청할수있는, 융합전공자격있나, 융합전공자격되나, 융합전공자격충족, 융합전공학점요구, 융합전공학점필요, 융합전공최소학점, 융합전공신청요건, 융합전공신청조건은, 융합전공필요한조건, 융합전공제한사항, 융합전공제약, 융합전공불가능한경우, 융합전공학년제한있나, 융합전공평점필요, 융합전공평점기준, 융합전공누구나가능, 융합전공모두가능, 융합전공신청돼, 융합전공돼, 융합전공가능해, 융합전공가능한가, 융합전공할수있나, 융합전공대상, 융합전공1학년, 융합전공편입생, 융합전공편입</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -849,7 +853,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>융합부전공자격, 융합부전공조건, 융합부전공가능, 융합부전공누가, 융합부전공몇학년, 융합부전공필요학점, 융합부전공평점, 융합부전공GPA, 융합부전공신청자격, 융합부전공지원자격, 융합부전공요건, 융합부전공신청할수있나, 융합부전공신청가능한가, 융합부전공신청할수있는, 융합부전공자격있나, 융합부전공자격되나, 융합부전공자격충족, 융합부전공학점요구, 융합부전공학점필요, 융합부전공최소학점, 융합부전공신청요건, 융합부전공신청조건은, 융합부전공필요한조건, 융합부전공제한사항, 융합부전공제약, 융합부전공불가능한경우, 융합부전공학년제한있나, 융합부전공평점필요, 융합부전공평점기준, 융합부전공누구나가능, 융합부전공모두가능</t>
+          <t>융합부전공자격, 융합부전공조건, 융합부전공가능, 융합부전공누가, 융합부전공몇학년, 융합부전공필요학점, 융합부전공평점, 융합부전공GPA, 융합부전공신청자격, 융합부전공지원자격, 융합부전공요건, 융합부전공신청할수있나, 융합부전공신청가능한가, 융합부전공신청할수있는, 융합부전공자격있나, 융합부전공자격되나, 융합부전공자격충족, 융합부전공학점요구, 융합부전공학점필요, 융합부전공최소학점, 융합부전공신청요건, 융합부전공신청조건은, 융합부전공필요한조건, 융합부전공제한사항, 융합부전공제약, 융합부전공불가능한경우, 융합부전공학년제한있나, 융합부전공평점필요, 융합부전공평점기준, 융합부전공누구나가능, 융합부전공모두가능, 융합부전공신청돼, 융합부전공돼, 융합부전공가능해, 융합부전공가능한가, 융합부전공할수있나, 융합부전공대상, 융합부전공1학년, 융합부전공편입생, 융합부전공편입</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -880,7 +884,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>연계전공자격, 연계전공조건, 연계전공가능, 연계전공누가, 연계전공몇학년, 연계전공필요학점, 연계전공평점, 연계전공GPA, 연계전공신청자격, 연계전공지원자격, 연계전공요건, 연계전공신청할수있나, 연계전공신청가능한가, 연계전공신청할수있는, 연계전공자격있나, 연계전공자격되나, 연계전공자격충족, 연계전공학점요구, 연계전공학점필요, 연계전공최소학점, 연계전공신청요건, 연계전공신청조건은, 연계전공필요한조건, 연계전공제한사항, 연계전공제약, 연계전공불가능한경우, 연계전공학년제한있나, 연계전공평점필요, 연계전공평점기준, 연계전공누구나가능, 연계전공모두가능</t>
+          <t>연계전공자격, 연계전공조건, 연계전공가능, 연계전공누가, 연계전공몇학년, 연계전공필요학점, 연계전공평점, 연계전공GPA, 연계전공신청자격, 연계전공지원자격, 연계전공요건, 연계전공신청할수있나, 연계전공신청가능한가, 연계전공신청할수있는, 연계전공자격있나, 연계전공자격되나, 연계전공자격충족, 연계전공학점요구, 연계전공학점필요, 연계전공최소학점, 연계전공신청요건, 연계전공신청조건은, 연계전공필요한조건, 연계전공제한사항, 연계전공제약, 연계전공불가능한경우, 연계전공학년제한있나, 연계전공평점필요, 연계전공평점기준, 연계전공누구나가능, 연계전공모두가능, 연계전공신청돼, 연계전공돼, 연계전공가능해, 연계전공가능한가, 연계전공할수있나, 연계전공대상, 연계전공1학년, 연계전공편입생, 연계전공편입</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -910,7 +914,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>소단위전공과정자격, 소단위전공과정조건, 소단위전공과정가능, 소단위전공과정누가, 소단위전공과정몇학년, 소단위전공과정필요학점, 소단위전공과정평점, 소단위전공과정GPA, 소단위전공과정신청자격, 소단위전공과정지원자격, 소단위전공과정요건, 소단위전공과정신청할수있나, 소단위전공과정신청가능한가, 소단위전공과정신청할수있는, 소단위전공과정자격있나, 소단위전공과정자격되나, 소단위전공과정자격충족, 소단위전공과정학점요구, 소단위전공과정학점필요, 소단위전공과정최소학점, 소단위전공과정신청요건, 소단위전공과정신청조건은, 소단위전공과정필요한조건, 소단위전공과정제한사항, 소단위전공과정제약, 소단위전공과정불가능한경우, 소단위전공과정학년제한있나, 소단위전공과정평점필요, 소단위전공과정평점기준, 소단위전공과정누구나가능, 소단위전공과정모두가능</t>
+          <t>소단위전공과정자격, 소단위전공과정조건, 소단위전공과정가능, 소단위전공과정누가, 소단위전공과정몇학년, 소단위전공과정필요학점, 소단위전공과정평점, 소단위전공과정GPA, 소단위전공과정신청자격, 소단위전공과정지원자격, 소단위전공과정요건, 소단위전공과정신청할수있나, 소단위전공과정신청가능한가, 소단위전공과정신청할수있는, 소단위전공과정자격있나, 소단위전공과정자격되나, 소단위전공과정자격충족, 소단위전공과정학점요구, 소단위전공과정학점필요, 소단위전공과정최소학점, 소단위전공과정신청요건, 소단위전공과정신청조건은, 소단위전공과정필요한조건, 소단위전공과정제한사항, 소단위전공과정제약, 소단위전공과정불가능한경우, 소단위전공과정학년제한있나, 소단위전공과정평점필요, 소단위전공과정평점기준, 소단위전공과정누구나가능, 소단위전공과정모두가능, 소단위전공과정신청돼, 소단위전공과정돼, 소단위전공과정가능해, 소단위전공과정가능한가, 소단위전공과정할수있나, 소단위전공과정대상, 소단위전공과정1학년, 소단위전공과정편입생, 소단위전공과정편입</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -944,7 +948,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>마이크로디그리자격, 마이크로디그리조건, 마이크로디그리가능, 마이크로디그리누가, 마이크로디그리몇학년, 마이크로디그리필요학점, 마이크로디그리평점, 마이크로디그리GPA, 마이크로디그리신청자격, 마이크로디그리지원자격, 마이크로디그리요건, 마이크로디그리신청할수있나, 마이크로디그리신청가능한가, 마이크로디그리신청할수있는, 마이크로디그리자격있나, 마이크로디그리자격되나, 마이크로디그리자격충족, 마이크로디그리학점요구, 마이크로디그리학점필요, 마이크로디그리최소학점, 마이크로디그리신청요건, 마이크로디그리신청조건은, 마이크로디그리필요한조건, 마이크로디그리제한사항, 마이크로디그리제약, 마이크로디그리불가능한경우, 마이크로디그리학년제한있나, 마이크로디그리평점필요, 마이크로디그리평점기준, 마이크로디그리누구나가능, 마이크로디그리모두가능</t>
+          <t>마이크로디그리자격, 마이크로디그리조건, 마이크로디그리가능, 마이크로디그리누가, 마이크로디그리몇학년, 마이크로디그리필요학점, 마이크로디그리평점, 마이크로디그리GPA, 마이크로디그리신청자격, 마이크로디그리지원자격, 마이크로디그리요건, 마이크로디그리신청할수있나, 마이크로디그리신청가능한가, 마이크로디그리신청할수있는, 마이크로디그리자격있나, 마이크로디그리자격되나, 마이크로디그리자격충족, 마이크로디그리학점요구, 마이크로디그리학점필요, 마이크로디그리최소학점, 마이크로디그리신청요건, 마이크로디그리신청조건은, 마이크로디그리필요한조건, 마이크로디그리제한사항, 마이크로디그리제약, 마이크로디그리불가능한경우, 마이크로디그리학년제한있나, 마이크로디그리평점필요, 마이크로디그리평점기준, 마이크로디그리누구나가능, 마이크로디그리모두가능, 마이크로디그리신청돼, 마이크로디그리돼, 마이크로디그리가능해, 마이크로디그리가능한가, 마이크로디그리할수있나, 마이크로디그리대상, 마이크로디그리1학년, 마이크로디그리편입생, 마이크로디그리편입, 누구나신청, 아무나, 아무나신청</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -978,7 +982,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>다전공취소, 다전공포기, 다전공포기절차, 다전공철회, 다전공그만, 다전공중단, 다전공해지, 다전공포기하고싶, 다전공포기하려면, 다전공포기방법, 다전공취소하려면, 다전공취소방법, 다전공취소하고싶, 다전공그만두고싶, 다전공중도포기, 다전공신청취소, 다전공철회방법, 다전공철회하려면, 다전공해지하려면, 다전공안하고싶, 다전공그만하고싶, 다전공중단하려면, 다전공포기가능, 다전공취소가능, 다전공언제까지포기, 다전공포기기한, 다전공취소기한</t>
+          <t>다전공취소, 다전공포기, 다전공포기절차, 다전공철회, 다전공그만, 다전공중단, 다전공해지, 다전공포기하고싶, 다전공포기하려면, 다전공포기방법, 다전공취소하려면, 다전공취소방법, 다전공취소하고싶, 다전공그만두고싶, 다전공중도포기, 다전공신청취소, 다전공철회방법, 다전공철회하려면, 다전공해지하려면, 다전공안하고싶, 다전공그만하고싶, 다전공중단하려면, 다전공포기가능, 다전공취소가능, 다전공언제까지포기, 다전공포기기한, 다전공취소기한, 다전공취소어떻게, 다전공포기어떻게, 다전공철회어떻게</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1012,7 +1016,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>복수전공취소, 복수전공포기, 복수전공포기절차, 복수전공철회, 복수전공그만, 복수전공중단, 복수전공해지, 복수전공포기하고싶, 복수전공포기하려면, 복수전공포기방법, 복수전공취소하려면, 복수전공취소방법, 복수전공취소하고싶, 복수전공그만두고싶, 복수전공중도포기, 복수전공신청취소, 복수전공철회방법, 복수전공철회하려면, 복수전공해지하려면, 복수전공안하고싶, 복수전공그만하고싶, 복수전공중단하려면, 복수전공포기가능, 복수전공취소가능, 복수전공언제까지포기, 복수전공포기기한, 복수전공취소기한</t>
+          <t>복수전공취소, 복수전공포기, 복수전공포기절차, 복수전공철회, 복수전공그만, 복수전공중단, 복수전공해지, 복수전공포기하고싶, 복수전공포기하려면, 복수전공포기방법, 복수전공취소하려면, 복수전공취소방법, 복수전공취소하고싶, 복수전공그만두고싶, 복수전공중도포기, 복수전공신청취소, 복수전공철회방법, 복수전공철회하려면, 복수전공해지하려면, 복수전공안하고싶, 복수전공그만하고싶, 복수전공중단하려면, 복수전공포기가능, 복수전공취소가능, 복수전공언제까지포기, 복수전공포기기한, 복수전공취소기한, 복수전공취소어떻게, 복수전공포기어떻게, 복수전공철회어떻게</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1046,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>부전공취소, 부전공포기, 부전공포기절차, 부전공철회, 부전공그만, 부전공중단, 부전공해지, 부전공포기하고싶, 부전공포기하려면, 부전공포기방법, 부전공취소하려면, 부전공취소방법, 부전공취소하고싶, 부전공그만두고싶, 부전공중도포기, 부전공신청취소, 부전공철회방법, 부전공철회하려면, 부전공해지하려면, 부전공안하고싶, 부전공그만하고싶, 부전공중단하려면, 부전공포기가능, 부전공취소가능, 부전공언제까지포기, 부전공포기기한, 부전공취소기한</t>
+          <t>부전공취소, 부전공포기, 부전공포기절차, 부전공철회, 부전공그만, 부전공중단, 부전공해지, 부전공포기하고싶, 부전공포기하려면, 부전공포기방법, 부전공취소하려면, 부전공취소방법, 부전공취소하고싶, 부전공그만두고싶, 부전공중도포기, 부전공신청취소, 부전공철회방법, 부전공철회하려면, 부전공해지하려면, 부전공안하고싶, 부전공그만하고싶, 부전공중단하려면, 부전공포기가능, 부전공취소가능, 부전공언제까지포기, 부전공포기기한, 부전공취소기한, 부전공취소어떻게, 부전공포기어떻게, 부전공철회어떻게</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1080,7 +1084,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>융합전공취소, 융합전공포기, 융합전공포기절차, 융합전공철회, 융합전공그만, 융합전공중단, 융합전공해지, 융합전공포기하고싶, 융합전공포기하려면, 융합전공포기방법, 융합전공취소하려면, 융합전공취소방법, 융합전공취소하고싶, 융합전공그만두고싶, 융합전공중도포기, 융합전공신청취소, 융합전공철회방법, 융합전공철회하려면, 융합전공해지하려면, 융합전공안하고싶, 융합전공그만하고싶, 융합전공중단하려면, 융합전공포기가능, 융합전공취소가능, 융합전공언제까지포기, 융합전공포기기한, 융합전공취소기한</t>
+          <t>융합전공취소, 융합전공포기, 융합전공포기절차, 융합전공철회, 융합전공그만, 융합전공중단, 융합전공해지, 융합전공포기하고싶, 융합전공포기하려면, 융합전공포기방법, 융합전공취소하려면, 융합전공취소방법, 융합전공취소하고싶, 융합전공그만두고싶, 융합전공중도포기, 융합전공신청취소, 융합전공철회방법, 융합전공철회하려면, 융합전공해지하려면, 융합전공안하고싶, 융합전공그만하고싶, 융합전공중단하려면, 융합전공포기가능, 융합전공취소가능, 융합전공언제까지포기, 융합전공포기기한, 융합전공취소기한, 융합전공취소어떻게, 융합전공포기어떻게, 융합전공철회어떻게</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1114,7 +1118,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>융합부전공취소, 융합부전공포기, 융합부전공포기절차, 융합부전공철회, 융합부전공그만, 융합부전공중단, 융합부전공해지, 융합부전공포기하고싶, 융합부전공포기하려면, 융합부전공포기방법, 융합부전공취소하려면, 융합부전공취소방법, 융합부전공취소하고싶, 융합부전공그만두고싶, 융합부전공중도포기, 융합부전공신청취소, 융합부전공철회방법, 융합부전공철회하려면, 융합부전공해지하려면, 융합부전공안하고싶, 융합부전공그만하고싶, 융합부전공중단하려면, 융합부전공포기가능, 융합부전공취소가능, 융합부전공언제까지포기, 융합부전공포기기한, 융합부전공취소기한</t>
+          <t>융합부전공취소, 융합부전공포기, 융합부전공포기절차, 융합부전공철회, 융합부전공그만, 융합부전공중단, 융합부전공해지, 융합부전공포기하고싶, 융합부전공포기하려면, 융합부전공포기방법, 융합부전공취소하려면, 융합부전공취소방법, 융합부전공취소하고싶, 융합부전공그만두고싶, 융합부전공중도포기, 융합부전공신청취소, 융합부전공철회방법, 융합부전공철회하려면, 융합부전공해지하려면, 융합부전공안하고싶, 융합부전공그만하고싶, 융합부전공중단하려면, 융합부전공포기가능, 융합부전공취소가능, 융합부전공언제까지포기, 융합부전공포기기한, 융합부전공취소기한, 융합부전공취소어떻게, 융합부전공포기어떻게, 융합부전공철회어떻게</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1148,7 +1152,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>연계전공취소, 연계전공포기, 연계전공포기절차, 연계전공철회, 연계전공그만, 연계전공중단, 연계전공해지, 연계전공포기하고싶, 연계전공포기하려면, 연계전공포기방법, 연계전공취소하려면, 연계전공취소방법, 연계전공취소하고싶, 연계전공그만두고싶, 연계전공중도포기, 연계전공신청취소, 연계전공철회방법, 연계전공철회하려면, 연계전공해지하려면, 연계전공안하고싶, 연계전공그만하고싶, 연계전공중단하려면, 연계전공포기가능, 연계전공취소가능, 연계전공언제까지포기, 연계전공포기기한, 연계전공취소기한</t>
+          <t>연계전공취소, 연계전공포기, 연계전공포기절차, 연계전공철회, 연계전공그만, 연계전공중단, 연계전공해지, 연계전공포기하고싶, 연계전공포기하려면, 연계전공포기방법, 연계전공취소하려면, 연계전공취소방법, 연계전공취소하고싶, 연계전공그만두고싶, 연계전공중도포기, 연계전공신청취소, 연계전공철회방법, 연계전공철회하려면, 연계전공해지하려면, 연계전공안하고싶, 연계전공그만하고싶, 연계전공중단하려면, 연계전공포기가능, 연계전공취소가능, 연계전공언제까지포기, 연계전공포기기한, 연계전공취소기한, 연계전공취소어떻게, 연계전공포기어떻게, 연계전공철회어떻게</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1182,7 +1186,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>소단위전공과정취소, 소단위전공과정포기, 소단위전공과정포기절차, 소단위전공과정철회, 소단위전공과정그만, 소단위전공과정중단, 소단위전공과정해지, 소단위전공과정포기하고싶, 소단위전공과정포기하려면, 소단위전공과정포기방법, 소단위전공과정취소하려면, 소단위전공과정취소방법, 소단위전공과정취소하고싶, 소단위전공과정그만두고싶, 소단위전공과정중도포기, 소단위전공과정신청취소, 소단위전공과정철회방법, 소단위전공과정철회하려면, 소단위전공과정해지하려면, 소단위전공과정안하고싶, 소단위전공과정그만하고싶, 소단위전공과정중단하려면, 소단위전공과정포기가능, 소단위전공과정취소가능, 소단위전공과정언제까지포기, 소단위전공과정포기기한, 소단위전공과정취소기한</t>
+          <t>소단위전공과정취소, 소단위전공과정포기, 소단위전공과정포기절차, 소단위전공과정철회, 소단위전공과정그만, 소단위전공과정중단, 소단위전공과정해지, 소단위전공과정포기하고싶, 소단위전공과정포기하려면, 소단위전공과정포기방법, 소단위전공과정취소하려면, 소단위전공과정취소방법, 소단위전공과정취소하고싶, 소단위전공과정그만두고싶, 소단위전공과정중도포기, 소단위전공과정신청취소, 소단위전공과정철회방법, 소단위전공과정철회하려면, 소단위전공과정해지하려면, 소단위전공과정안하고싶, 소단위전공과정그만하고싶, 소단위전공과정중단하려면, 소단위전공과정포기가능, 소단위전공과정취소가능, 소단위전공과정언제까지포기, 소단위전공과정포기기한, 소단위전공과정취소기한, 소단위전공과정취소어떻게, 소단위전공과정포기어떻게, 소단위전공과정철회어떻게</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1220,7 +1224,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>마이크로디그리취소, 마이크로디그리포기, 마이크로디그리포기절차, 마이크로디그리철회, 마이크로디그리그만, 마이크로디그리중단, 마이크로디그리해지, 마이크로디그리포기하고싶, 마이크로디그리포기하려면, 마이크로디그리포기방법, 마이크로디그리취소하려면, 마이크로디그리취소방법, 마이크로디그리취소하고싶, 마이크로디그리그만두고싶, 마이크로디그리중도포기, 마이크로디그리신청취소, 마이크로디그리철회방법, 마이크로디그리철회하려면, 마이크로디그리해지하려면, 마이크로디그리안하고싶, 마이크로디그리그만하고싶, 마이크로디그리중단하려면, 마이크로디그리포기가능, 마이크로디그리취소가능, 마이크로디그리언제까지포기, 마이크로디그리포기기한, 마이크로디그리취소기한</t>
+          <t>마이크로디그리취소, 마이크로디그리포기, 마이크로디그리포기절차, 마이크로디그리철회, 마이크로디그리그만, 마이크로디그리중단, 마이크로디그리해지, 마이크로디그리포기하고싶, 마이크로디그리포기하려면, 마이크로디그리포기방법, 마이크로디그리취소하려면, 마이크로디그리취소방법, 마이크로디그리취소하고싶, 마이크로디그리그만두고싶, 마이크로디그리중도포기, 마이크로디그리신청취소, 마이크로디그리철회방법, 마이크로디그리철회하려면, 마이크로디그리해지하려면, 마이크로디그리안하고싶, 마이크로디그리그만하고싶, 마이크로디그리중단하려면, 마이크로디그리포기가능, 마이크로디그리취소가능, 마이크로디그리언제까지포기, 마이크로디그리포기기한, 마이크로디그리취소기한, 마이크로디그리취소어떻게, 마이크로디그리포기어떻게, 마이크로디그리철회어떻게</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1258,7 +1262,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>다전공변경, 다전공을변경, 다전공바꾸, 다전공을바꾸, 다전공전환, 다전공을전환, 다전공교체, 다전공을교체, 다전공수정, 다전공을수정, 다전공변경하려, 다전공변경가능, 다전공변경방법, 다전공바꿀수있, 다전공전환가능, 다전공교체가능, 다전공다른걸로, 다전공변경하고싶, 다전공바꾸고싶, 다전공전환하고싶, 다전공언제변경, 다전공변경기한, 다전공변경절차, 다전공다시신청, 다전공재신청, 다전공다른전공으로, 다전공전공바꾸기, 다전공전공교체</t>
+          <t>다전공변경, 다전공을변경, 다전공바꾸, 다전공을바꾸, 다전공전환, 다전공을전환, 다전공교체, 다전공을교체, 다전공수정, 다전공을수정, 다전공변경하려, 다전공변경가능, 다전공변경방법, 다전공바꿀수있, 다전공전환가능, 다전공교체가능, 다전공다른걸로, 다전공변경하고싶, 다전공바꾸고싶, 다전공전환하고싶, 다전공언제변경, 다전공변경기한, 다전공변경절차, 다전공다시신청, 다전공재신청, 다전공다른전공으로, 다전공전공바꾸기, 다전공전공교체, 다전공바꿀수있어, 다전공바꿀수있나, 다전공전공변경, 다전공전공바꿀</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1290,7 +1294,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>복수전공변경, 복수전공을변경, 복수전공바꾸, 복수전공을바꾸, 복수전공전환, 복수전공을전환, 복수전공교체, 복수전공을교체, 복수전공수정, 복수전공을수정, 복수전공변경하려, 복수전공변경가능, 복수전공변경방법, 복수전공바꿀수있, 복수전공전환가능, 복수전공교체가능, 복수전공다른걸로, 복수전공변경하고싶, 복수전공바꾸고싶, 복수전공전환하고싶, 복수전공언제변경, 복수전공변경기한, 복수전공변경절차, 복수전공다시신청, 복수전공재신청, 복수전공다른전공으로, 복수전공전공바꾸기, 복수전공전공교체</t>
+          <t>복수전공변경, 복수전공을변경, 복수전공바꾸, 복수전공을바꾸, 복수전공전환, 복수전공을전환, 복수전공교체, 복수전공을교체, 복수전공수정, 복수전공을수정, 복수전공변경하려, 복수전공변경가능, 복수전공변경방법, 복수전공바꿀수있, 복수전공전환가능, 복수전공교체가능, 복수전공다른걸로, 복수전공변경하고싶, 복수전공바꾸고싶, 복수전공전환하고싶, 복수전공언제변경, 복수전공변경기한, 복수전공변경절차, 복수전공다시신청, 복수전공재신청, 복수전공다른전공으로, 복수전공전공바꾸기, 복수전공전공교체, 복수전공바꿀수있어, 복수전공바꿀수있나, 복수전공전공변경, 복수전공전공바꿀</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1322,7 +1326,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>부전공변경, 부전공을변경, 부전공바꾸, 부전공을바꾸, 부전공전환, 부전공을전환, 부전공교체, 부전공을교체, 부전공수정, 부전공을수정, 부전공변경하려, 부전공변경가능, 부전공변경방법, 부전공바꿀수있, 부전공전환가능, 부전공교체가능, 부전공다른걸로, 부전공변경하고싶, 부전공바꾸고싶, 부전공전환하고싶, 부전공언제변경, 부전공변경기한, 부전공변경절차, 부전공다시신청, 부전공재신청, 부전공다른전공으로, 부전공전공바꾸기, 부전공전공교체</t>
+          <t>부전공변경, 부전공을변경, 부전공바꾸, 부전공을바꾸, 부전공전환, 부전공을전환, 부전공교체, 부전공을교체, 부전공수정, 부전공을수정, 부전공변경하려, 부전공변경가능, 부전공변경방법, 부전공바꿀수있, 부전공전환가능, 부전공교체가능, 부전공다른걸로, 부전공변경하고싶, 부전공바꾸고싶, 부전공전환하고싶, 부전공언제변경, 부전공변경기한, 부전공변경절차, 부전공다시신청, 부전공재신청, 부전공다른전공으로, 부전공전공바꾸기, 부전공전공교체, 부전공바꿀수있어, 부전공바꿀수있나, 부전공전공변경, 부전공전공바꿀</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1354,7 +1358,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>융합전공변경, 융합전공바꾸, 융합전공전환, 융합전공교체, 융합전공수정, 융합전공변경하려, 융합전공을변경, 융합전공을바꾸, 융합전공을전환, 융합전공을교체, 융합전공을수정, 융합전공변경가능, 융합전공변경방법, 융합전공바꿀수있, 융합전공전환가능, 융합전공교체가능, 융합전공다른걸로, 융합전공변경하고싶, 융합전공바꾸고싶, 융합전공전환하고싶, 융합전공언제변경, 융합전공변경기한, 융합전공변경절차, 융합전공다시신청, 융합전공재신청, 융합전공다른전공으로, 융합전공전공바꾸기, 융합전공전공교체</t>
+          <t>융합전공변경, 융합전공바꾸, 융합전공전환, 융합전공교체, 융합전공수정, 융합전공변경하려, 융합전공을변경, 융합전공을바꾸, 융합전공을전환, 융합전공을교체, 융합전공을수정, 융합전공변경가능, 융합전공변경방법, 융합전공바꿀수있, 융합전공전환가능, 융합전공교체가능, 융합전공다른걸로, 융합전공변경하고싶, 융합전공바꾸고싶, 융합전공전환하고싶, 융합전공언제변경, 융합전공변경기한, 융합전공변경절차, 융합전공다시신청, 융합전공재신청, 융합전공다른전공으로, 융합전공전공바꾸기, 융합전공전공교체, 융합전공바꿀수있어, 융합전공바꿀수있나, 융합전공전공변경, 융합전공전공바꿀</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1386,7 +1390,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>융합부전공변경, 융합부전공바꾸, 융합부전공전환, 융합부전공교체, 융합부전공수정, 융합부전공변경하려, 융합부전공을변경, 융합부전공을바꾸, 융합부전공을전환, 융합부전공을교체, 융합부전공을수정, 융합부전공변경가능, 융합부전공변경방법, 융합부전공바꿀수있, 융합부전공전환가능, 융합부전공교체가능, 융합부전공다른걸로, 융합부전공변경하고싶, 융합부전공바꾸고싶, 융합부전공전환하고싶, 융합부전공언제변경, 융합부전공변경기한, 융합부전공변경절차, 융합부전공다시신청, 융합부전공재신청, 융합부전공다른전공으로, 융합부전공전공바꾸기, 융합부전공전공교체</t>
+          <t>융합부전공변경, 융합부전공바꾸, 융합부전공전환, 융합부전공교체, 융합부전공수정, 융합부전공변경하려, 융합부전공을변경, 융합부전공을바꾸, 융합부전공을전환, 융합부전공을교체, 융합부전공을수정, 융합부전공변경가능, 융합부전공변경방법, 융합부전공바꿀수있, 융합부전공전환가능, 융합부전공교체가능, 융합부전공다른걸로, 융합부전공변경하고싶, 융합부전공바꾸고싶, 융합부전공전환하고싶, 융합부전공언제변경, 융합부전공변경기한, 융합부전공변경절차, 융합부전공다시신청, 융합부전공재신청, 융합부전공다른전공으로, 융합부전공전공바꾸기, 융합부전공전공교체, 융합부전공바꿀수있어, 융합부전공바꿀수있나, 융합부전공전공변경, 융합부전공전공바꿀</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1418,7 +1422,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>연계전공변경, 연계전공바꾸, 연계전공전환, 연계전공교체, 연계전공수정, 연계전공변경하려, 연계전공을변경, 연계전공을바꾸, 연계전공을전환, 연계전공을교체, 연계전공을수정, 연계전공변경가능, 연계전공변경방법, 연계전공바꿀수있, 연계전공전환가능, 연계전공교체가능, 연계전공다른걸로, 연계전공변경하고싶, 연계전공바꾸고싶, 연계전공전환하고싶, 연계전공언제변경, 연계전공변경기한, 연계전공변경절차, 연계전공다시신청, 연계전공재신청, 연계전공다른전공으로, 연계전공전공바꾸기, 연계전공전공교체</t>
+          <t>연계전공변경, 연계전공바꾸, 연계전공전환, 연계전공교체, 연계전공수정, 연계전공변경하려, 연계전공을변경, 연계전공을바꾸, 연계전공을전환, 연계전공을교체, 연계전공을수정, 연계전공변경가능, 연계전공변경방법, 연계전공바꿀수있, 연계전공전환가능, 연계전공교체가능, 연계전공다른걸로, 연계전공변경하고싶, 연계전공바꾸고싶, 연계전공전환하고싶, 연계전공언제변경, 연계전공변경기한, 연계전공변경절차, 연계전공다시신청, 연계전공재신청, 연계전공다른전공으로, 연계전공전공바꾸기, 연계전공전공교체, 연계전공바꿀수있어, 연계전공바꿀수있나, 연계전공전공변경, 연계전공전공바꿀</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1450,7 +1454,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>소단위전공과정변경, 소단위전공과정바꾸, 소단위전공과정전환, 소단위전공과정교체, 소단위전공과정수정, 소단위전공과정변경하려, 소단위전공과정을변경, 소단위전공과정을바꾸, 소단위전공과정을전환, 소단위전공과정을교체, 소단위전공과정을수정, 소단위전공과정변경가능, 소단위전공과정변경방법, 소단위전공과정바꿀수있, 소단위전공과정전환가능, 소단위전공과정교체가능, 소단위전공과정다른걸로, 소단위전공과정변경하고싶, 소단위전공과정바꾸고싶, 소단위전공과정전환하고싶, 소단위전공과정언제변경, 소단위전공과정변경기한, 소단위전공과정변경절차, 소단위전공과정다시신청, 소단위전공과정재신청, 소단위전공과정다른전공으로, 소단위전공과정전공바꾸기, 소단위전공과정전공교체</t>
+          <t>소단위전공과정변경, 소단위전공과정바꾸, 소단위전공과정전환, 소단위전공과정교체, 소단위전공과정수정, 소단위전공과정변경하려, 소단위전공과정을변경, 소단위전공과정을바꾸, 소단위전공과정을전환, 소단위전공과정을교체, 소단위전공과정을수정, 소단위전공과정변경가능, 소단위전공과정변경방법, 소단위전공과정바꿀수있, 소단위전공과정전환가능, 소단위전공과정교체가능, 소단위전공과정다른걸로, 소단위전공과정변경하고싶, 소단위전공과정바꾸고싶, 소단위전공과정전환하고싶, 소단위전공과정언제변경, 소단위전공과정변경기한, 소단위전공과정변경절차, 소단위전공과정다시신청, 소단위전공과정재신청, 소단위전공과정다른전공으로, 소단위전공과정전공바꾸기, 소단위전공과정전공교체, 소단위전공과정바꿀수있어, 소단위전공과정바꿀수있나, 소단위전공과정전공변경, 소단위전공과정전공바꿀</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1486,7 +1490,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>마이크로디그리변경, 마이크로디그리바꾸, 마이크로디그리전환, 마이크로디그리교체, 마이크로디그리수정, 마이크로디그리변경하려, 마이크로디그리을변경, 마이크로디그리을바꾸, 마이크로디그리을전환, 마이크로디그리을교체, 마이크로디그리을수정, 마이크로디그리변경가능, 마이크로디그리변경방법, 마이크로디그리바꿀수있, 마이크로디그리전환가능, 마이크로디그리교체가능, 마이크로디그리다른걸로, 마이크로디그리변경하고싶, 마이크로디그리바꾸고싶, 마이크로디그리전환하고싶, 마이크로디그리언제변경, 마이크로디그리변경기한, 마이크로디그리변경절차, 마이크로디그리다시신청, 마이크로디그리재신청, 마이크로디그리다른전공으로, 마이크로디그리전공바꾸기, 마이크로디그리전공교체</t>
+          <t>마이크로디그리변경, 마이크로디그리바꾸, 마이크로디그리전환, 마이크로디그리교체, 마이크로디그리수정, 마이크로디그리변경하려, 마이크로디그리을변경, 마이크로디그리을바꾸, 마이크로디그리을전환, 마이크로디그리을교체, 마이크로디그리을수정, 마이크로디그리변경가능, 마이크로디그리변경방법, 마이크로디그리바꿀수있, 마이크로디그리전환가능, 마이크로디그리교체가능, 마이크로디그리다른걸로, 마이크로디그리변경하고싶, 마이크로디그리바꾸고싶, 마이크로디그리전환하고싶, 마이크로디그리언제변경, 마이크로디그리변경기한, 마이크로디그리변경절차, 마이크로디그리다시신청, 마이크로디그리재신청, 마이크로디그리다른전공으로, 마이크로디그리전공바꾸기, 마이크로디그리전공교체, 마이크로디그리바꿀수있어, 마이크로디그리바꿀수있나, 마이크로디그리전공변경, 마이크로디그리전공바꿀</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1791,7 +1795,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>마이크로디그리차이, 마이크로디그리비교, 마이크로디그리다른점, 마이크로디그리vs, 마이크로디그리뭐가, 마이크로디그리어떤차이, 마이크로디그리어떤, 마이크로디그리차이점, 마이크로디그리비교해줘, 마이크로디그리뭐가다른, 마이크로디그리어떤게나, 마이크로디그리어떤게좋, 마이크로디그리차이가뭐, 마이크로디그리장단점, 마이크로디그리유리한, 마이크로디그리불리한, 마이크로디그리선택하려면, 마이크로디그리고민중, 마이크로디그리어떤걸선택, 마이크로디그리구분, 마이크로디그리구별, 마이크로디그리차이알려줘, 마이크로디그리비교분석, 마이크로디그리비교해서, 마이크로디그리대조</t>
+          <t>똑같아, 같은거야, 같은건가, 차이, 다른거야, 뭐가달라, 마이크로디그리소단위, 소단위마이크로</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2587,7 +2591,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>성적처리, 수강, 수강철회, 수강신청, 수강취소, 수강변경, 수강정정, 수강신청방법, 철회방법, 철회가능, 드랍, 수강드랍, 과목취소, 성적이상, 성적문의, 성적정정</t>
+          <t>성적처리, 수강, 수강철회, 수강신청, 수강취소, 수강변경, 수강정정, 수강신청방법, 철회방법, 철회가능, 드랍, 수강드랍, 과목취소, 성적이상, 성적문의, 성적정정, 이의신청, 성적이의, 성적이의신청</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3083,7 +3087,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>마이크로디그리 소단위전공과정 똑같아,마이크로디그리 소단위전공과정 같은거,마이크로디그리 소단위전공과정 차이,소단위전공과정 마이크로디그리 뭐가달라,마이크로디그리 소단위 같은건가,마이크로디그리 소단위 다른거야</t>
+          <t>똑같아, 같은거야, 같은건가, 차이, 다른거야, 뭐가달라, 마이크로디그리소단위, 소단위마이크로</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,7 +664,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>nan, 소단위전공과정신청기간</t>
+          <t>소단위전공과정신청, 소단위전공과정기간, 소단위전공과정신청기간, 소단위전공과정언제, 소단위전공과정마감, 소단위전공과정신청일, 소단위전공과정접수, 소단위전공과정접수일, 소단위전공과정몇월, 소단위전공과정일정, 소단위전공과정날짜, 소단위전공과정데드라인, 소단위전공과정시기, 소단위전공과정지원, 소단위전공과정시작, 소단위전공과정마감일, 소단위전공과정기한, 소단위전공과정수강신청, 소단위전공과정신청할수있, 소단위전공과정신청마감언제, 소단위전공과정신청시작언제, 소단위전공과정몇학년부터, 소단위전공과정학년제한, 소단위전공과정학기언제</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>똑같아, 같은거야, 같은건가, 차이, 다른거야, 뭐가달라, 마이크로디그리소단위, 소단위마이크로</t>
+          <t>같은거야, 같은건가, 다른거야, 똑같아, 마이크로디그리소단위, 뭐가달라, 소단위마이크로, 차이</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>등록금, 수강료, 추가 등록금, 학비, 납부, 추가등록금, 감면, 면제, 장학금, 환불, 고지, 등록금고지, 고지서, 학비얼마, 비용얼마, 추가비용, 추가학비, 더내야하나, 등록금추가, 등록금더, 등록금별도, 돈얼마</t>
+          <t>등록금, 수강료, 추가 등록금, 학비, 납부, 추가등록금, 감면, 면제, 장학금, 환불, 고지, 등록금고지, 고지서, 학비얼마, 비용얼마, 추가비용, 추가학비, 더내야하나, 등록금추가, 등록금더, 등록금별도, 돈얼마, 비용</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2834,7 +2834,11 @@
           <t>다전공신청, 다전공접수, 다전공방법, 다전공신청방법, 다전공어떻게, 다전공절차, 다전공신청과정, 다전공과정, 다전공신청서, 다전공서류, 다전공제출, 다전공지원, 다전공지원방법, 다전공등록, 다전공수강신청, 다전공신청하는방법, 다전공신청할수있, 다전공신청하려면, 다전공신청방법알려, 다전공어떻게신청, 다전공신청하는법, 다전공신청절차는, 다전공온라인신청, 다전공오프라인신청, 다전공신청서류, 다전공신청서제출</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>등록금, 학비, 수강료</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>📋 신청 절차:
@@ -2867,7 +2871,11 @@
           <t>복수전공신청, 복수전공접수, 복수전공방법, 복수전공신청방법, 복수전공어떻게, 복수전공절차, 복수전공신청과정, 복수전공과정, 복수전공신청서, 복수전공서류, 복수전공제출, 복수전공지원, 복수전공지원방법, 복수전공등록, 복수전공수강신청, 복수전공신청하는방법, 복수전공신청할수있, 복수전공신청하려면, 복수전공신청방법알려, 복수전공어떻게신청, 복수전공신청하는법, 복수전공신청절차는, 복수전공온라인신청, 복수전공오프라인신청, 복수전공신청서류, 복수전공신청서제출</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>등록금, 학비, 수강료</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>📋 신청 절차:
@@ -2900,7 +2908,11 @@
           <t>부전공신청, 부전공접수, 부전공방법, 부전공신청방법, 부전공어떻게, 부전공절차, 부전공신청과정, 부전공과정, 부전공신청서, 부전공서류, 부전공제출, 부전공지원, 부전공지원방법, 부전공등록, 부전공수강신청, 부전공신청하는방법, 부전공신청할수있, 부전공신청하려면, 부전공신청방법알려, 부전공어떻게신청, 부전공신청하는법, 부전공신청절차는, 부전공온라인신청, 부전공오프라인신청, 부전공신청서류, 부전공신청서제출</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>등록금, 학비, 수강료</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>📋 신청 절차:
@@ -2933,7 +2945,11 @@
           <t>융합전공신청, 융합전공접수, 융합전공방법, 융합전공신청방법, 융합전공어떻게, 융합전공절차, 융합전공신청과정, 융합전공과정, 융합전공신청서, 융합전공서류, 융합전공제출, 융합전공지원, 융합전공지원방법, 융합전공등록, 융합전공수강신청, 융합전공신청하는방법, 융합전공신청할수있, 융합전공신청하려면, 융합전공신청방법알려, 융합전공어떻게신청, 융합전공신청하는법, 융합전공신청절차는, 융합전공온라인신청, 융합전공오프라인신청, 융합전공신청서류, 융합전공신청서제출</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>등록금, 학비, 수강료</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>📋 신청 절차:
@@ -2965,7 +2981,11 @@
           <t>융합부전공신청, 융합부전공접수, 융합부전공방법, 융합부전공신청방법, 융합부전공어떻게, 융합부전공절차, 융합부전공신청과정, 융합부전공과정, 융합부전공신청서, 융합부전공서류, 융합부전공제출, 융합부전공지원, 융합부전공지원방법, 융합부전공등록, 융합부전공수강신청, 융합부전공신청하는방법, 융합부전공신청할수있, 융합부전공신청하려면, 융합부전공신청방법알려, 융합부전공어떻게신청, 융합부전공신청하는법, 융합부전공신청절차는, 융합부전공온라인신청, 융합부전공오프라인신청, 융합부전공신청서류, 융합부전공신청서제출</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>등록금, 학비, 수강료</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>📋 신청 절차:
@@ -2997,7 +3017,11 @@
           <t>연계전공신청, 연계전공접수, 연계전공방법, 연계전공신청방법, 연계전공어떻게, 연계전공절차, 연계전공신청과정, 연계전공과정, 연계전공신청서, 연계전공서류, 연계전공제출, 연계전공지원, 연계전공지원방법, 연계전공등록, 연계전공수강신청, 연계전공신청하는방법, 연계전공신청할수있, 연계전공신청하려면, 연계전공신청방법알려, 연계전공어떻게신청, 연계전공신청하는법, 연계전공신청절차는, 연계전공온라인신청, 연계전공오프라인신청, 연계전공신청서류, 연계전공신청서제출</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>등록금, 학비, 수강료</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>📋 신청 절차:
@@ -3027,10 +3051,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>소단위전공과정신청, 소단위전공과정기간, 소단위전공과정신청기간, 소단위전공과정언제, 소단위전공과정마감, 소단위전공과정신청일, 소단위전공과정접수, 소단위전공과정접수일, 소단위전공과정몇월, 소단위전공과정일정, 소단위전공과정날짜, 소단위전공과정데드라인, 소단위전공과정시기, 소단위전공과정방법, 소단위전공과정신청방법, 소단위전공과정어떻게, 소단위전공과정절차, 소단위전공과정신청과정, 소단위전공과정과정, 소단위전공과정신청서, 소단위전공과정서류, 소단위전공과정제출, 소단위전공과정지원, 소단위전공과정지원방법, 소단위전공과정등록, 소단위전공과정시작, 소단위전공과정마감일, 소단위전공과정기한, 소단위전공과정수강신청, 소단위전공과정신청하는방법, 소단위전공과정신청할수있, 소단위전공과정신청하려면, 소단위전공과정신청방법알려, 소단위전공과정어떻게신청, 소단위전공과정신청하는법, 소단위전공과정신청절차는, 소단위전공과정온라인신청, 소단위전공과정오프라인신청, 소단위전공과정신청서류, 소단위전공과정신청서제출, 소단위전공과정신청마감언제, 소단위전공과정신청시작언제, 소단위전공과정몇학년부터, 소단위전공과정학년제한, 소단위전공과정학기언제</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>소단위전공과정신청, 소단위전공과정접수, 소단위전공과정방법, 소단위전공과정신청방법, 소단위전공과정어떻게, 소단위전공과정절차, 소단위전공과정신청과정, 소단위전공과정과정, 소단위전공과정신청서, 소단위전공과정서류, 소단위전공과정제출, 소단위전공과정지원, 소단위전공과정지원방법, 소단위전공과정등록, 소단위전공과정수강신청, 소단위전공과정신청하는방법, 소단위전공과정신청할수있, 소단위전공과정신청하려면, 소단위전공과정신청방법알려, 소단위전공과정어떻게신청, 소단위전공과정신청하는법, 소단위전공과정신청절차는, 소단위전공과정온라인신청, 소단위전공과정오프라인신청, 소단위전공과정신청서류, 소단위전공과정신청서제출</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>등록금, 학비, 수강료</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>📋 신청 절차:
@@ -3062,7 +3090,11 @@
           <t>마이크로디그리신청, 마이크로디그리접수, 마이크로디그리방법, 마이크로디그리신청방법, 마이크로디그리어떻게, 마이크로디그리절차, 마이크로디그리신청과정, 마이크로디그리과정, 마이크로디그리신청서, 마이크로디그리서류, 마이크로디그리제출, 마이크로디그리지원, 마이크로디그리지원방법, 마이크로디그리등록, 마이크로디그리수강신청, 마이크로디그리신청하는방법, 마이크로디그리신청할수있, 마이크로디그리신청하려면, 마이크로디그리신청방법알려, 마이크로디그리어떻게신청, 마이크로디그리신청하는법, 마이크로디그리신청절차는, 마이크로디그리온라인신청, 마이크로디그리오프라인신청, 마이크로디그리신청서류, 마이크로디그리신청서제출</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>등록금, 학비, 수강료</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>📋 신청 절차:
@@ -3073,33 +3105,6 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>PROGRAM_COMPARISON</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>마이크로디그리</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>똑같아, 같은거야, 같은건가, 차이, 다른거야, 뭐가달라, 마이크로디그리소단위, 소단위마이크로</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>✅ 마이크로디그리와 소단위전공과정은 같은 제도입니다!
-📌 정식 명칭은 **소단위전공과정**이며, **마이크로디그리(Micro Degree, MD)**는 같은 제도의 줄임말/별칭입니다.
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는
-💡 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -2594,7 +2594,11 @@
           <t>성적처리, 수강, 수강철회, 수강신청, 수강취소, 수강변경, 수강정정, 수강신청방법, 철회방법, 철회가능, 드랍, 수강드랍, 과목취소, 성적이상, 성적문의, 성적정정, 이의신청, 성적이의, 성적이의신청</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>계절학기, 여름학기, 겨울학기</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>📝 수강 관련 안내

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3109,6 +3109,240 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>F075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CONCURRENT_ENROLL</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>다전공</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>동시이수,중복신청,중복이수,동시신청,이중전공,병행가능,같이신청,함께신청,같이할수,함께할수,동시에할수,두개같이,두가지같이,겸할수</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>📋 다전공 동시 이수 규정:
+✅ 가능한 조합:
+• 복수전공 + 마이크로디그리
+• 부전공 + 마이크로디그리
+• 융합전공 + 마이크로디그리
+• 융합부전공 + 마이크로디그리
+• 연계전공 + 마이크로디그리
+• 마이크로디그리 여러 개 중복 이수
+❌ 불가능한 조합:
+• 복수전공 + 부전공
+• 복수전공 + 융합전공
+• 복수전공 + 연계전공
+• 부전공 + 융합전공
+• 부전공 + 연계전공
+• 융합전공 + 연계전공
+💡 요약: 마이크로디그리만 중복 신청이 가능하며, 나머지 다전공(복수전공, 부전공, 융합전공, 융합부전공, 연계전공)은 1개만 이수할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>F076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CONCURRENT_ENROLL</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>복수전공동시,복수전공같이,복수전공함께,복수전공겸,복수전공병행,복수전공중복,복수전공이중,복전동시,복전같이,복전함께,복수전공동시이수,복수전공중복신청</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>📋 복수전공 동시 이수 안내:
+✅ 가능: 복수전공 + 마이크로디그리 (마이크로디그리는 여러 개도 가능)
+❌ 불가: 복수전공 + 부전공, 복수전공 + 융합전공, 복수전공 + 연계전공
+💡 복수전공을 포함한 다전공은 1개만 이수 가능하며, 마이크로디그리만 추가로 병행할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>F077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CONCURRENT_ENROLL</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>부전공</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>부전공동시,부전공같이,부전공함께,부전공겸,부전공병행,부전공중복,부전공이중,부전동시,부전같이,부전함께,부전공동시이수,부전공중복신청</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>📋 부전공 동시 이수 안내:
+✅ 가능: 부전공 + 마이크로디그리 (마이크로디그리는 여러 개도 가능)
+❌ 불가: 부전공 + 복수전공, 부전공 + 융합전공, 부전공 + 연계전공
+💡 부전공을 포함한 다전공은 1개만 이수 가능하며, 마이크로디그리만 추가로 병행할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>F078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CONCURRENT_ENROLL</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>융합전공</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>융합전공동시,융합전공같이,융합전공함께,융합전공겸,융합전공병행,융합전공중복,융합전공이중,융합전공동시이수,융합전공중복신청</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>📋 융합전공 동시 이수 안내:
+✅ 가능: 융합전공 + 마이크로디그리 (마이크로디그리는 여러 개도 가능)
+❌ 불가: 융합전공 + 복수전공, 융합전공 + 부전공, 융합전공 + 연계전공
+💡 융합전공을 포함한 다전공은 1개만 이수 가능하며, 마이크로디그리만 추가로 병행할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>F079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CONCURRENT_ENROLL</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>융합부전공</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>융합부전공동시,융합부전공같이,융합부전공함께,융합부전공겸,융합부전공병행,융합부전공중복,융합부전공이중,융합부전공동시이수,융합부전공중복신청</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>📋 융합부전공 동시 이수 안내:
+✅ 가능: 융합부전공 + 마이크로디그리 (마이크로디그리는 여러 개도 가능)
+❌ 불가: 융합부전공 + 복수전공, 융합부전공 + 부전공, 융합부전공 + 연계전공
+💡 융합부전공을 포함한 다전공은 1개만 이수 가능하며, 마이크로디그리만 추가로 병행할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>F080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CONCURRENT_ENROLL</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>연계전공</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>연계전공동시,연계전공같이,연계전공함께,연계전공겸,연계전공병행,연계전공중복,연계전공이중,연계전공동시이수,연계전공중복신청</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>📋 연계전공 동시 이수 안내:
+✅ 가능: 연계전공 + 마이크로디그리 (마이크로디그리는 여러 개도 가능)
+❌ 불가: 연계전공 + 복수전공, 연계전공 + 부전공, 연계전공 + 융합전공
+💡 연계전공을 포함한 다전공은 1개만 이수 가능하며, 마이크로디그리만 추가로 병행할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>F081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CONCURRENT_ENROLL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>마이크로디그리</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>마이크로디그리동시,마이크로디그리같이,마이크로디그리함께,마이크로디그리겸,마이크로디그리병행,마이크로디그리중복,마이크로디그리이중,마이크로디그리여러개,마이크로디그리두개,md동시,md같이,md중복,마이크로디그리동시이수,마이크로디그리중복신청</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>📋 마이크로디그리 동시 이수 안내:
+✅ 마이크로디그리는 다른 모든 다전공과 동시 이수 가능합니다!
+• 복수전공 + 마이크로디그리 ✅
+• 부전공 + 마이크로디그리 ✅
+• 융합전공 + 마이크로디그리 ✅
+• 융합부전공 + 마이크로디그리 ✅
+• 연계전공 + 마이크로디그리 ✅
+• 마이크로디그리 + 마이크로디그리 ✅ (여러 개 중복 가능)
+💡 마이크로디그리는 유일하게 중복 신청이 가능한 다전공 제도입니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724D7EFA-10C8-47FC-A23F-6BBB9BB956FF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -620,97 +626,6 @@
   </si>
   <si>
     <t>등록금, 학비, 수강료</t>
-  </si>
-  <si>
-    <t>📅 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
-💡 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>✅ 다전공 신청 자격: 한경국립대학교 재학생이면 누구나 신청 가능
-📌 모든 다전공 제도는 입학 후 첫 학기부터 신청 가능
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는
-💡 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
-  </si>
-  <si>
-    <t>✅ 다전공 신청 자격: 입학 후 첫 학기부터 재학생이면 누구나 신청 가능
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는
-💡 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
-  </si>
-  <si>
-    <t>✅ 다전공 신청 자격: 입학 후 첫 학기부터 재학생이면 누구나 신청 가능
-📌 단, 신입생은 2020학번 이후부터, 편입생은 2022학번 이후부터 신청 가능
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는
-💡 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
-  </si>
-  <si>
-    <t>📋 다전공 포기 절차:
-1. 포기서 작성
-2. 다전공 학부장 확인
-3. 다전공 사무실에 제출
-📌 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
-⏰ 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
-💡 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 복수전공 포기 절차:
-1. 포기서 작성
-2. 복수전공 학부장 확인
-3. 복수전공 사무실에 제출
-📌 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
-⏰ 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
-💡 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 부전공 포기 절차:
-1. 포기서 작성
-2. 부전공 학부장 확인
-3. 부전공 사무실에 제출
-📌 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
-⏰ 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
-💡 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 융합전공 포기 절차:
-1. 포기서 작성
-2. 융합전공 학부장 확인
-3. 융합전공 사무실에 제출
-📌 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
-⏰ 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
-💡 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 융합부전공 포기 절차:
-1. 포기서 작성
-2. 융합부전공 학부장 확인
-3. 융합부전공 사무실에 제출
-📌 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
-⏰ 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
-💡 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 연계전공 포기 절차:
-1. 포기서 작성
-2. 연계전공 학부장 확인
-3. 연계전공 사무실에 제출
-📌 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
-⏰ 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
-💡 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 소단위전공과정(마이크로디그리) 포기 절차:
-1. 포기서 작성
-2. 소단위전공과정 교육운영전공 학부장 확인
-3. 교육운영전공 사무실에 제출
-📌 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
-⏰ 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
-💡 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 다전공 변경 절차:
-1. 기존 다전공의 포기서 제출 (해당 전공 사무실)
-2. 새로 하려는 다전공의 신청서 제출 (해당 전공 사무실)
-📌 다전공 신청 기간에 포기와 신청을 동시에 할 수 있음
-💡 포기서 양식 등은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
   </si>
   <si>
     <t>📊 다전공 제도 비교
@@ -829,22 +744,6 @@
 ▸ 소단위전공과정(마이크로디그리) - 8~12학점, 이수증 발급
 💡 각 제도별 자세한 내용은 '복수전공이 뭐야?' 처럼 질문해주세요!
  💡 세부사항은 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
-    <t>📚 복수전공이란?
-원전공 이외에 다른 전공의 전공과정을 이수하여 2개의 학위를 인정받는 제도입니다.
-📊 이수학점:
-▸ 원전공: 전필 포함 39학점 이상 (인문사회계열(법학전공 제외) 36학점)
-▸ 복수전공: 전필 포함 39학점 이상 (인문사회계열(법학전공 제외) 36학점)
-✅ 졸업 시 2개의 학위 취득 가능!
-📋 신청 가능한 전공 (총 43개):
-▸ 인문사회 계열 (10개): 경영학, 영미언어문화, 행정학, 법학, 문예창작미디어콘텐츠홍보 등
-▸ 자연과학 계열 (7개): 식품영양학, 동물생명과학, 조경학, 의류산업학 등
-▸ 공학 계열 (20개): 컴퓨터공학, 전자공학, 기계공학, 건축학, 소프트웨어융합 등
-▸ 예체능 계열 (6개): 스포츠과학, 시각미디어디자인, 실용음악학 등
-※ 원전공을 제외한 모든 전공에 신청 가능
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
   </si>
   <si>
     <t>📚 부전공이란?
@@ -859,47 +758,6 @@
 ▸ 공학 계열 (20개): 컴퓨터공학, 전자공학, 기계공학, 건축학, 소프트웨어융합 등
 ▸ 예체능 계열 (6개): 스포츠과학, 시각미디어디자인, 실용음악학 등
 ※ 원전공을 제외한 모든 전공에 신청 가능
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
-    <t>📚 융합전공이란?
-2개 이상의 전공이 융합하여 새로운 전공을 만든 것으로, 학생들에게 보다 나은 교육의 질을 제공하기 위해 만들어진 전공입니다.
-📋 융합전공 종류:
-▸ 스마트헬스케어융합전공
-▸ AI스마트팜융합전공
-▸ AI빅데이터융합전공
-▸ 공공헬스케어IT융합전공
-▸ 반도체융합전공
-▸ 스마트애그리푸드시스템전공
-▸ 탄소중립바이오시스템융합전공
-✅ 2개의 학위 인정!
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
-    <t>📚 융합부전공이란?
-2개 이상의 전공이 융합하여 새로운 전공을 만든 것으로, 융합전공의 부전공 버전입니다.
-📋 융합부전공 종류:
-▸ 스마트헬스케어융합전공
-▸ AI스마트팜융합전공
-▸ AI빅데이터융합전공
-▸ 공공헬스케어IT융합전공
-▸ 반도체융합전공
-▸ 스마트애그리푸드시스템전공
-▸ 탄소중립바이오시스템융합전공
-✅ 융합전공보다 학점 부담이 적어 상대적으로 이수하기 쉬움!
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
-    <t>📚 연계전공이란?
-원전공 이외에 다른 전공에서 정한 교과목을 이수하는 제도입니다.
-대학생들에게 다양한 전공 선택 기회를 제공하는 새로운 전공 이수방법입니다.
-📊 이수학점:
-▸ 원전공: 전필 포함 78학점 이상 (인문사회계열 72학점)
-▸ 연계전공: 전공 교과목 9학점 이상
-✅ 적은 학점(9학점)으로 도전해 보기 좋은 제도!
 💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
  💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
   </si>
@@ -923,68 +781,6 @@
 💡 자세한 사항은 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
   </si>
   <si>
-    <t>📊 다전공별 이수학점 안내
-▸ 복수전공: 원전공 39*학점 + 복수전공 39*학점 * 인문사회계열(법학전공 제외) 36학점
-▸ 부전공: 원전공 51*학점 + 부전공 27학점 * 인문사회계열(법학전공 제외) 48학점
-▸ 융합전공: 원전공 39*학점 + 융합전공 39학점 * 인문사회계열(법학전공 제외) 36학점
-▸ 융합부전공: 원전공 51*학점 + 융합부전공 27학점 * 인문사회계열(법학전공 제외) 48학점
-▸ 연계전공: 원전공 78학점 + 연계전공 9학점 (인문사회계열 72학점)
-▸ 마이크로디그리: 과정별 8~12학점
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
-    <t>📊 복수전공 이수학점
-▸ 원전공: 전필 포함 39*학점 이상 * 인문사회계열(법학전공 제외) 36학점
-▸ 복수전공: 전필 포함 39*학점 이상 * 인문사회계열(법학전공 제외) 36학점
-📌 교양: 원전공 졸업요구학점 이상 이수
-📌 졸업인증: 원전공만 합격
-📌 졸업종합시험: 원전공 및 복수전공 둘 다 합격 필요
-⚠️ 인문계열 → 자연/공학계열 복수전공 시 총 졸업학점 수 증가 가능
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
-    <t>📊 부전공 이수학점
-▸ 원전공: 전필 포함 51*학점 이상 * 인문사회계열(법학전공 제외) 36학점
-▸ 부전공: 전필 포함 27학점 이상
-📌 교양: 원전공 졸업요구학점 이상 이수
-📌 졸업인증: 원전공만 합격
-📌 졸업종합시험: 원전공만 합격
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
-    <t>📊 융합전공 이수학점
-▸ 원전공: 전필 포함 39*학점 이상 * 인문사회계열(법학전공 제외) 36학점
-▸ 융합전공: 전필 포함 39학점 이상
-📌 교양: 원전공 졸업요구학점 이상 이수
-📌 졸업인증: 원전공만 합격
-📌 졸업종합시험: 원전공 및 융합전공 둘 다 합격 필요
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
-    <t>📊 융합부전공 이수학점
-▸ 원전공: 전필 포함 51*학점 이상 * 인문사회계열(법학전공 제외) 48학점
-▸ 융합부전공: 전필 포함 27학점 이상
-📌 교양: 원전공 졸업요구학점 이상 이수
-📌 졸업인증: 원전공만 합격
-📌 졸업종합시험: 원전공만 합격
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
-    <t>📊 연계전공 이수학점
-▸ 원전공: 전필 포함 78학점 이상 (인문사회계열 72학점)
-▸ 연계전공: 전공 교과목 9학점 이상
-📌 교양: 원전공 졸업요구학점 이상 이수
-📌 졸업인증: 원전공만 합격
-📌 졸업종합시험: 원전공만 합격
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown 또는 
- 💡 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
-  </si>
-  <si>
     <t>📊 소단위전공과정(마이크로디그리) 이수학점
 ▸ 과정별 편성된 과목 3~4과목 (8~12학점) 이수
 📌 원전공 전공과목과 동일한 교과목: 원전공 이수구분으로 인정
@@ -1005,21 +801,6 @@
 ✅ 이수 시 별도의 이수증 발급
 💡 세부 과정은 '마이크로디그리 목록 알려줘'라고 질문해주세요!
 💡 자세한 사항은  왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
-  </si>
-  <si>
-    <t>💰 등록금 안내
-▸ 원전공 기준의 등록금을 납부하면 됨
-▸ 다전공을 신청해도 추가 등록금 없음!
-▸ 다전공 제도 참여 시 별도 장학금 지원은 현재 없음
-💡 등록금 고지, 환불 등은 학교 홈페이지 참조: https://www.hknu.ac.kr/bbs/kor/69/87311/artclView.do?layout=unknown
-📞 재무팀: 031-670-5476</t>
-  </si>
-  <si>
-    <t>🎓 졸업식 일정
-▸ 전기 졸업식: 매년 2월 중순
-▸ 후기 졸업식: 매년 8월 중순
-💡 정확한 일정은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/87507/artclView.do?layout=unknown
-📞 학사지원팀: 031-670-5036</t>
   </si>
   <si>
     <t>📄 증명서 발급 안내
@@ -1132,77 +913,6 @@
 📞 학사지원팀: 031-670-5032</t>
   </si>
   <si>
-    <t>📋 신청 절차:
-1. 신청서 작성
-2. 다전공 지도교수 및 학부장 확인
-3. 다전공 희망 학부장 확인
-4. 다전공 희망전공 사무실에 제출
-💡 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 신청 절차:
-1. 신청서 작성
-2. 복수전공 지도교수 및 학부장 확인
-3. 복수전공 희망 학부장 확인
-4. 복수전공 희망전공 사무실에 제출
-💡 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 신청 절차:
-1. 신청서 작성
-2. 부전공 지도교수 및 학부장 확인
-3. 부전공 희망 학부장 확인
-4. 부전공 희망전공 사무실에 제출
-💡 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 신청 절차:
-1. 신청서 작성
-2. 원전공 지도교수 및 학부장 확인
-3. 융합전공 학부장 확인 및 제출(제1공학관 222호)
-💡 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 신청 절차:
-1. 신청서 작성
-2. 원전공 지도교수 및 학부장 확인
-3. 융합부전공 학부장 확인 및 제출(제1공학관 222호)
-💡 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 신청 절차:
-1. 신청서 작성
-2. 원전공 지도교수 및 학부장 확인
-3. 연계전공 희망 학부장 확인
-4. 연계전공 희망전공 사무실에 제출
-💡 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 신청 절차:
-1. 신청서 작성
-2. 교육운영전공 지도교수 및 학부장 확인
-3. 교육운영전공 학부장 확인 및 사무실 제출
-💡 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/90689/artclView.do?layout=unknown</t>
-  </si>
-  <si>
-    <t>📋 다전공 동시 이수 규정:
-✅ 가능한 조합:
-• 복수전공 + 마이크로디그리
-• 부전공 + 마이크로디그리
-• 융합전공 + 마이크로디그리
-• 융합부전공 + 마이크로디그리
-• 연계전공 + 마이크로디그리
-• 마이크로디그리 여러 개 중복 이수
-❌ 불가능한 조합:
-• 복수전공 + 부전공
-• 복수전공 + 융합전공
-• 복수전공 + 연계전공
-• 부전공 + 융합전공
-• 부전공 + 연계전공
-• 융합전공 + 연계전공
-💡 요약: 마이크로디그리만 중복 신청이 가능하며, 나머지 다전공(복수전공, 부전공, 융합전공, 융합부전공, 연계전공)은 1개만 이수할 수 있습니다.</t>
-  </si>
-  <si>
     <t>📋 복수전공 동시 이수 안내:
 ✅ 가능: 복수전공 + 마이크로디그리 (마이크로디그리는 여러 개도 가능)
 ❌ 불가: 복수전공 + 부전공, 복수전공 + 융합전공, 복수전공 + 연계전공
@@ -1244,20 +954,3696 @@
 💡 마이크로디그리는 유일하게 중복 신청이 가능한 다전공 제도입니다.</t>
   </si>
   <si>
-    <t>📅 학사일정(개강일, 종강일, 시험기간, 방학 등)은 학교 홈페이지에서 확인하세요.
-🔗 학사일정 바로가기: https://www.hknu.ac.kr/kor/646/subview.do
-💡 이 챗봇은 다전공·유연학사 제도 전용입니다. 학사일정 관련 자세한 문의는 학사지원팀(031-670-5035)으로 연락해 주세요.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 자격: 한경국립대학교 재학생이면 누구나 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 모든 다전공 제도는 입학 후 첫 학기부터 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 자격: 입학 후 첫 학기부터 재학생이면 누구나 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 자격: 입학 후 첫 학기부터 재학생이면 누구나 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 단, 신입생은 2020학번 이후부터, 편입생은 2022학번 이후부터 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 포기 절차:
+1. 포기서 작성
+2. 다전공 학부장 확인
+3. 다전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 복수전공 포기 절차:
+1. 포기서 작성
+2. 복수전공 학부장 확인
+3. 복수전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 부전공 포기 절차:
+1. 포기서 작성
+2. 부전공 학부장 확인
+3. 부전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합전공 포기 절차:
+1. 포기서 작성
+2. 융합전공 학부장 확인
+3. 융합전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합부전공 포기 절차:
+1. 포기서 작성
+2. 융합부전공 학부장 확인
+3. 융합부전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 연계전공 포기 절차:
+1. 포기서 작성
+2. 연계전공 학부장 확인
+3. 연계전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 소단위전공과정(마이크로디그리) 포기 절차:
+1. 포기서 작성
+2. 소단위전공과정 교육운영전공 학부장 확인
+3. 교육운영전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이미 취득한 학점(이수 중인 과목은 성적 확정 후)의 이수구분은 자유선택으로 변경됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기는 별도의 신청 기간 없이 해당 사무실에 제출 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기서 양식은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 변경 절차:
+1. 기존 다전공의 포기서 제출 (해당 전공 사무실)
+2. 새로 하려는 다전공의 신청서 제출 (해당 전공 사무실)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 기간에 포기와 신청을 동시에 할 수 있음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 포기서 양식 등은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 복수전공이란?
+원전공 이외에 다른 전공의 전공과정을 이수하여 2개의 학위를 인정받는 제도입니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수학점:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공: 전필 포함 39학점 이상 (인문사회계열(법학전공 제외) 36학점)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 복수전공: 전필 포함 39학점 이상 (인문사회계열(법학전공 제외) 36학점)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업 시 2개의 학위 취득 가능!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 가능한 전공 (총 43개):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 인문사회 계열 (10개): 경영학, 영미언어문화, 행정학, 법학, 문예창작미디어콘텐츠홍보 등
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자연과학 계열 (7개): 식품영양학, 동물생명과학, 조경학, 의류산업학 등
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 공학 계열 (20개): 컴퓨터공학, 전자공학, 기계공학, 건축학, 소프트웨어융합 등
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 예체능 계열 (6개): 스포츠과학, 시각미디어디자인, 실용음악학 등
+※ 원전공을 제외한 모든 전공에 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합전공이란?
+2개 이상의 전공이 융합하여 새로운 전공을 만든 것으로, 학생들에게 보다 나은 교육의 질을 제공하기 위해 만들어진 전공입니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합전공 종류:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 스마트헬스케어융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI스마트팜융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI빅데이터융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 공공헬스케어IT융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 반도체융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 스마트애그리푸드시스템전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 탄소중립바이오시스템융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2개의 학위 인정!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합부전공이란?
+2개 이상의 전공이 융합하여 새로운 전공을 만든 것으로, 융합전공의 부전공 버전입니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합부전공 종류:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 스마트헬스케어융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI스마트팜융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI빅데이터융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 공공헬스케어IT융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 반도체융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 스마트애그리푸드시스템전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 탄소중립바이오시스템융합전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합전공보다 학점 부담이 적어 상대적으로 이수하기 쉬움!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 연계전공이란?
+원전공 이외에 다른 전공에서 정한 교과목을 이수하는 제도입니다.
+대학생들에게 다양한 전공 선택 기회를 제공하는 새로운 전공 이수방법입니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수학점:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공: 전필 포함 78학점 이상 (인문사회계열 72학점)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 연계전공: 전공 교과목 9학점 이상
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 적은 학점(9학점)으로 도전해 보기 좋은 제도!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공별 이수학점 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 복수전공: 원전공 39*학점 + 복수전공 39*학점 * 인문사회계열(법학전공 제외) 36학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 부전공: 원전공 51*학점 + 부전공 27학점 * 인문사회계열(법학전공 제외) 48학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합전공: 원전공 39*학점 + 융합전공 39학점 * 인문사회계열(법학전공 제외) 36학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합부전공: 원전공 51*학점 + 융합부전공 27학점 * 인문사회계열(법학전공 제외) 48학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 연계전공: 원전공 78학점 + 연계전공 9학점 (인문사회계열 72학점)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 마이크로디그리: 과정별 8~12학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 복수전공 이수학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공: 전필 포함 39*학점 이상 * 인문사회계열(법학전공 제외) 36학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 복수전공: 전필 포함 39*학점 이상 * 인문사회계열(법학전공 제외) 36학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교양: 원전공 졸업요구학점 이상 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업인증: 원전공만 합격
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업종합시험: 원전공 및 복수전공 둘 다 합격 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 인문계열 → 자연/공학계열 복수전공 시 총 졸업학점 수 증가 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 부전공 이수학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공: 전필 포함 51*학점 이상 * 인문사회계열(법학전공 제외) 36학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 부전공: 전필 포함 27학점 이상
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교양: 원전공 졸업요구학점 이상 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업인증: 원전공만 합격
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업종합시험: 원전공만 합격
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합전공 이수학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공: 전필 포함 39*학점 이상 * 인문사회계열(법학전공 제외) 36학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합전공: 전필 포함 39학점 이상
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교양: 원전공 졸업요구학점 이상 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업인증: 원전공만 합격
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업종합시험: 원전공 및 융합전공 둘 다 합격 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합부전공 이수학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공: 전필 포함 51*학점 이상 * 인문사회계열(법학전공 제외) 48학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 융합부전공: 전필 포함 27학점 이상
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교양: 원전공 졸업요구학점 이상 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업인증: 원전공만 합격
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업종합시험: 원전공만 합격
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 연계전공 이수학점
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공: 전필 포함 78학점 이상 (인문사회계열 72학점)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 연계전공: 전공 교과목 9학점 이상
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교양: 원전공 졸업요구학점 이상 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업인증: 원전공만 합격
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업종합시험: 원전공만 합격
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 및 '다전공 비교 분석' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 등록금 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공 기준의 등록금을 납부하면 됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공을 신청해도 추가 등록금 없음!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 제도 참여 시 별도 장학금 지원은 현재 없음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 등록금 고지, 환불 등은 학교 홈페이지 참조: https://www.hknu.ac.kr/bbs/kor/69/94055/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 재무팀: 031-670-5476</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🎓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업식 일정
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전기 졸업식: 매년 2월 중순
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 후기 졸업식: 매년 8월 중순
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 정확한 일정은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/92840/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사지원팀: 031-670-5036</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 절차:
+1. 신청서 작성
+2. 다전공 지도교수 및 학부장 확인
+3. 다전공 희망 학부장 확인
+4. 다전공 희망전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 절차:
+1. 신청서 작성
+2. 복수전공 지도교수 및 학부장 확인
+3. 복수전공 희망 학부장 확인
+4. 복수전공 희망전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 절차:
+1. 신청서 작성
+2. 부전공 지도교수 및 학부장 확인
+3. 부전공 희망 학부장 확인
+4. 부전공 희망전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 절차:
+1. 신청서 작성
+2. 원전공 지도교수 및 학부장 확인
+3. 융합전공 학부장 확인 및 제출(제1공학관 222호)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 절차:
+1. 신청서 작성
+2. 원전공 지도교수 및 학부장 확인
+3. 융합부전공 학부장 확인 및 제출(제1공학관 222호)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 절차:
+1. 신청서 작성
+2. 원전공 지도교수 및 학부장 확인
+3. 연계전공 희망 학부장 확인
+4. 연계전공 희망전공 사무실에 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 절차:
+1. 신청서 작성
+2. 교육운영전공 지도교수 및 학부장 확인
+3. 교육운영전공 학부장 확인 및 사무실 제출
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식은 학사공지에서 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 동시 이수 규정:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 가능한 조합:
+• 복수전공 + 마이크로디그리
+• 부전공 + 마이크로디그리
+• 융합전공 + 마이크로디그리
+• 융합부전공 + 마이크로디그리
+• 연계전공 + 마이크로디그리
+• 마이크로디그리 여러 개 중복 이수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>❌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 불가능한 조합:
+• 복수전공 + 부전공
+• 복수전공 + 융합전공
+• 복수전공 + 연계전공
+• 부전공 + 융합전공
+• 부전공 + 연계전공
+• 융합전공 + 연계전공
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 요약: 마이크로디그리만 중복 신청이 가능하며, 나머지 다전공(복수전공, 부전공, 융합전공, 융합부전공, 연계전공)은 1개만 이수할 수 있습니다.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사일정(개강일, 종강일, 시험기간, 방학 등)은 학교 홈페이지에서 확인하세요.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사일정 바로가기: https://www.hknu.ac.kr/kor/646/subview.do
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이 챗봇은 다전공·유연학사 제도 전용입니다. 학사일정 관련 자세한 문의는 학사지원팀(031-670-5032)으로 연락해 주세요.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1265,9 +4651,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1305,22 +4724,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1362,7 +4790,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1394,9 +4822,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1428,6 +4874,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1603,11 +5067,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1627,7 +5091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1643,11 +5107,11 @@
       <c r="E2" t="s">
         <v>198</v>
       </c>
-      <c r="F2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1663,11 +5127,11 @@
       <c r="E3" t="s">
         <v>198</v>
       </c>
-      <c r="F3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="F3" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1683,11 +5147,11 @@
       <c r="E4" t="s">
         <v>198</v>
       </c>
-      <c r="F4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1703,11 +5167,11 @@
       <c r="E5" t="s">
         <v>198</v>
       </c>
-      <c r="F5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1723,11 +5187,11 @@
       <c r="E6" t="s">
         <v>198</v>
       </c>
-      <c r="F6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1743,11 +5207,11 @@
       <c r="E7" t="s">
         <v>198</v>
       </c>
-      <c r="F7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1763,11 +5227,11 @@
       <c r="E8" t="s">
         <v>198</v>
       </c>
-      <c r="F8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1783,11 +5247,11 @@
       <c r="E9" t="s">
         <v>198</v>
       </c>
-      <c r="F9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1800,11 +5264,11 @@
       <c r="D10" t="s">
         <v>124</v>
       </c>
-      <c r="F10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1817,11 +5281,11 @@
       <c r="D11" t="s">
         <v>125</v>
       </c>
-      <c r="F11" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1834,11 +5298,11 @@
       <c r="D12" t="s">
         <v>126</v>
       </c>
-      <c r="F12" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="F12" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1851,11 +5315,11 @@
       <c r="D13" t="s">
         <v>127</v>
       </c>
-      <c r="F13" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1868,11 +5332,11 @@
       <c r="D14" t="s">
         <v>128</v>
       </c>
-      <c r="F14" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="F14" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1885,11 +5349,11 @@
       <c r="D15" t="s">
         <v>129</v>
       </c>
-      <c r="F15" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="F15" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1905,11 +5369,11 @@
       <c r="E16" t="s">
         <v>199</v>
       </c>
-      <c r="F16" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="F16" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1925,11 +5389,11 @@
       <c r="E17" t="s">
         <v>199</v>
       </c>
-      <c r="F17" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="F17" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1942,11 +5406,11 @@
       <c r="D18" t="s">
         <v>132</v>
       </c>
-      <c r="F18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="F18" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1959,11 +5423,11 @@
       <c r="D19" t="s">
         <v>133</v>
       </c>
-      <c r="F19" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="F19" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1976,11 +5440,11 @@
       <c r="D20" t="s">
         <v>134</v>
       </c>
-      <c r="F20" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="F20" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1993,11 +5457,11 @@
       <c r="D21" t="s">
         <v>135</v>
       </c>
-      <c r="F21" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="F21" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -2010,11 +5474,11 @@
       <c r="D22" t="s">
         <v>136</v>
       </c>
-      <c r="F22" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="F22" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -2027,11 +5491,11 @@
       <c r="D23" t="s">
         <v>137</v>
       </c>
-      <c r="F23" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="F23" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -2047,11 +5511,11 @@
       <c r="E24" t="s">
         <v>199</v>
       </c>
-      <c r="F24" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="F24" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -2067,11 +5531,11 @@
       <c r="E25" t="s">
         <v>199</v>
       </c>
-      <c r="F25" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="F25" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -2084,11 +5548,11 @@
       <c r="D26" t="s">
         <v>140</v>
       </c>
-      <c r="F26" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="F26" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -2101,11 +5565,11 @@
       <c r="D27" t="s">
         <v>141</v>
       </c>
-      <c r="F27" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="F27" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -2118,11 +5582,11 @@
       <c r="D28" t="s">
         <v>142</v>
       </c>
-      <c r="F28" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="F28" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -2135,11 +5599,11 @@
       <c r="D29" t="s">
         <v>143</v>
       </c>
-      <c r="F29" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="F29" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -2152,11 +5616,11 @@
       <c r="D30" t="s">
         <v>144</v>
       </c>
-      <c r="F30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="F30" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -2169,11 +5633,11 @@
       <c r="D31" t="s">
         <v>145</v>
       </c>
-      <c r="F31" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="F31" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2189,11 +5653,11 @@
       <c r="E32" t="s">
         <v>199</v>
       </c>
-      <c r="F32" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="F32" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -2209,11 +5673,11 @@
       <c r="E33" t="s">
         <v>199</v>
       </c>
-      <c r="F33" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="F33" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2226,11 +5690,11 @@
       <c r="D34" t="s">
         <v>148</v>
       </c>
-      <c r="F34" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="F34" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -2243,11 +5707,11 @@
       <c r="D35" t="s">
         <v>149</v>
       </c>
-      <c r="F35" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="F35" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -2260,11 +5724,11 @@
       <c r="D36" t="s">
         <v>150</v>
       </c>
-      <c r="F36" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="F36" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -2280,11 +5744,11 @@
       <c r="E37" t="s">
         <v>110</v>
       </c>
-      <c r="F37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="F37" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -2300,11 +5764,11 @@
       <c r="E38" t="s">
         <v>109</v>
       </c>
-      <c r="F38" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="F38" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -2317,11 +5781,11 @@
       <c r="D39" t="s">
         <v>153</v>
       </c>
-      <c r="F39" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="F39" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -2337,11 +5801,11 @@
       <c r="E40" t="s">
         <v>199</v>
       </c>
-      <c r="F40" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="F40" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -2357,11 +5821,11 @@
       <c r="E41" t="s">
         <v>199</v>
       </c>
-      <c r="F41" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="F41" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -2374,11 +5838,11 @@
       <c r="D42" t="s">
         <v>156</v>
       </c>
-      <c r="F42" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="F42" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -2391,11 +5855,11 @@
       <c r="D43" t="s">
         <v>157</v>
       </c>
-      <c r="F43" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="F43" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -2408,11 +5872,11 @@
       <c r="D44" t="s">
         <v>158</v>
       </c>
-      <c r="F44" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="F44" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -2425,11 +5889,11 @@
       <c r="D45" t="s">
         <v>159</v>
       </c>
-      <c r="F45" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="F45" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -2442,11 +5906,11 @@
       <c r="D46" t="s">
         <v>160</v>
       </c>
-      <c r="F46" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="F46" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -2459,11 +5923,11 @@
       <c r="D47" t="s">
         <v>161</v>
       </c>
-      <c r="F47" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="F47" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -2476,11 +5940,11 @@
       <c r="D48" t="s">
         <v>162</v>
       </c>
-      <c r="F48" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="F48" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -2496,11 +5960,11 @@
       <c r="E49" t="s">
         <v>199</v>
       </c>
-      <c r="F49" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="F49" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -2513,11 +5977,11 @@
       <c r="D50" t="s">
         <v>164</v>
       </c>
-      <c r="F50" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="F50" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -2530,11 +5994,11 @@
       <c r="D51" t="s">
         <v>165</v>
       </c>
-      <c r="F51" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="F51" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -2547,11 +6011,11 @@
       <c r="D52" t="s">
         <v>166</v>
       </c>
-      <c r="F52" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="F52" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -2564,11 +6028,11 @@
       <c r="D53" t="s">
         <v>167</v>
       </c>
-      <c r="F53" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="F53" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -2581,11 +6045,11 @@
       <c r="D54" t="s">
         <v>168</v>
       </c>
-      <c r="F54" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="F54" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -2598,11 +6062,11 @@
       <c r="D55" t="s">
         <v>169</v>
       </c>
-      <c r="F55" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="F55" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -2618,11 +6082,11 @@
       <c r="E56" t="s">
         <v>199</v>
       </c>
-      <c r="F56" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="F56" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -2638,11 +6102,11 @@
       <c r="E57" t="s">
         <v>199</v>
       </c>
-      <c r="F57" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="F57" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -2655,11 +6119,11 @@
       <c r="D58" t="s">
         <v>172</v>
       </c>
-      <c r="F58" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="F58" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -2672,11 +6136,11 @@
       <c r="D59" t="s">
         <v>173</v>
       </c>
-      <c r="F59" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="F59" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -2689,11 +6153,11 @@
       <c r="D60" t="s">
         <v>174</v>
       </c>
-      <c r="F60" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="F60" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -2706,11 +6170,11 @@
       <c r="D61" t="s">
         <v>175</v>
       </c>
-      <c r="F61" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="F61" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -2726,11 +6190,11 @@
       <c r="E62" t="s">
         <v>200</v>
       </c>
-      <c r="F62" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="F62" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -2743,11 +6207,11 @@
       <c r="D63" t="s">
         <v>177</v>
       </c>
-      <c r="F63" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="F63" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -2760,11 +6224,11 @@
       <c r="D64" t="s">
         <v>178</v>
       </c>
-      <c r="F64" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="F64" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -2780,11 +6244,11 @@
       <c r="E65" t="s">
         <v>199</v>
       </c>
-      <c r="F65" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="F65" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -2800,11 +6264,11 @@
       <c r="E66" t="s">
         <v>199</v>
       </c>
-      <c r="F66" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="F66" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -2817,11 +6281,11 @@
       <c r="D67" t="s">
         <v>181</v>
       </c>
-      <c r="F67" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="F67" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -2837,11 +6301,11 @@
       <c r="E68" t="s">
         <v>201</v>
       </c>
-      <c r="F68" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="F68" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -2857,11 +6321,11 @@
       <c r="E69" t="s">
         <v>201</v>
       </c>
-      <c r="F69" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="F69" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -2877,11 +6341,11 @@
       <c r="E70" t="s">
         <v>201</v>
       </c>
-      <c r="F70" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="F70" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -2897,11 +6361,11 @@
       <c r="E71" t="s">
         <v>201</v>
       </c>
-      <c r="F71" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="F71" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -2917,11 +6381,11 @@
       <c r="E72" t="s">
         <v>201</v>
       </c>
-      <c r="F72" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="F72" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -2937,11 +6401,11 @@
       <c r="E73" t="s">
         <v>201</v>
       </c>
-      <c r="F73" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="F73" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -2957,11 +6421,11 @@
       <c r="E74" t="s">
         <v>201</v>
       </c>
-      <c r="F74" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="F74" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -2977,11 +6441,11 @@
       <c r="E75" t="s">
         <v>201</v>
       </c>
-      <c r="F75" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="F75" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -2994,11 +6458,11 @@
       <c r="D76" t="s">
         <v>190</v>
       </c>
-      <c r="F76" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="F76" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -3011,11 +6475,11 @@
       <c r="D77" t="s">
         <v>191</v>
       </c>
-      <c r="F77" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="F77" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -3028,11 +6492,11 @@
       <c r="D78" t="s">
         <v>192</v>
       </c>
-      <c r="F78" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="F78" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -3045,11 +6509,11 @@
       <c r="D79" t="s">
         <v>193</v>
       </c>
-      <c r="F79" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="F79" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -3062,11 +6526,11 @@
       <c r="D80" t="s">
         <v>194</v>
       </c>
-      <c r="F80" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="F80" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>85</v>
       </c>
@@ -3079,11 +6543,11 @@
       <c r="D81" t="s">
         <v>195</v>
       </c>
-      <c r="F81" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="F81" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -3096,11 +6560,11 @@
       <c r="D82" t="s">
         <v>196</v>
       </c>
-      <c r="F82" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="F82" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -3113,11 +6577,13 @@
       <c r="D83" t="s">
         <v>197</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" s="2" t="s">
         <v>262</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A618688D-3FA3-46BF-878C-B2705769857E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF50044-1501-4CBA-B8FE-665D46FD123C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,10 +55,6 @@
     <t>가능,되나,포기,취소</t>
   </si>
   <si>
-    <t>📅 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
-💡 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
-  </si>
-  <si>
     <t>F002</t>
   </si>
   <si>
@@ -129,12 +125,6 @@
   </si>
   <si>
     <t>다전공자격, 다전공조건, 다전공가능, 다전공누가, 다전공몇학년, 다전공필요학점, 다전공평점, 다전공GPA, 다전공신청자격, 다전공지원자격, 다전공요건, 다전공신청할수있나, 다전공신청가능한가, 다전공신청할수있는, 다전공자격있나, 다전공자격되나, 다전공자격충족, 다전공학점요구, 다전공학점필요, 다전공최소학점, 다전공신청요건, 다전공신청조건은, 다전공필요한조건, 다전공제한사항, 다전공제약, 다전공불가능한경우, 다전공학년제한있나, 다전공평점필요, 다전공평점기준, 다전공누구나가능, 다전공모두가능, 다전공신청돼, 다전공돼, 다전공가능해, 다전공가능한가, 다전공할수있나, 다전공대상, 다전공1학년, 다전공편입생, 다전공편입</t>
-  </si>
-  <si>
-    <t>✅ 다전공 신청 자격: 한경국립대학교 재학생이면 누구나 신청 가능
-📌 모든 다전공 제도는 입학 후 첫 학기부터 신청 가능
-💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는
-💡 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
   </si>
   <si>
     <t>F010</t>
@@ -1497,6 +1487,98 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 자격: 한경국립대학교 재학생이면 누구나 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 모든 다전공 제도는 입학 후 첫 학기부터 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown 또는
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>📅 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
+📌 2026-2학기 유연학사제도(다전공) 모집 1차 신청기간: 2026. 4. 1.(수) ∽ 4.10.(금)
+💡 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1581,12 +1663,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1964,1580 +2047,1580 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
+      <c r="F2" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
+      <c r="F3" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
-        <v>11</v>
+      <c r="F4" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
-        <v>11</v>
+      <c r="F5" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
-        <v>11</v>
+      <c r="F6" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" t="s">
-        <v>11</v>
+      <c r="F7" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="F8" t="s">
-        <v>11</v>
+      <c r="F8" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" t="s">
-        <v>11</v>
+      <c r="F9" s="3" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="s">
         <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" t="s">
         <v>49</v>
       </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" t="s">
-        <v>51</v>
-      </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" t="s">
         <v>58</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" t="s">
         <v>61</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" t="s">
         <v>64</v>
-      </c>
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" t="s">
         <v>67</v>
-      </c>
-      <c r="B22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" t="s">
         <v>70</v>
-      </c>
-      <c r="B23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" t="s">
-        <v>71</v>
-      </c>
-      <c r="F23" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" t="s">
         <v>73</v>
-      </c>
-      <c r="B24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" t="s">
         <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F27" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" t="s">
         <v>79</v>
-      </c>
-      <c r="C28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" t="s">
         <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" t="s">
         <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" t="s">
-        <v>89</v>
-      </c>
-      <c r="F30" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" t="s">
         <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" t="s">
-        <v>91</v>
-      </c>
-      <c r="F31" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" t="s">
         <v>79</v>
-      </c>
-      <c r="C32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" t="s">
-        <v>93</v>
-      </c>
-      <c r="E32" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" t="s">
         <v>79</v>
-      </c>
-      <c r="C33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" t="s">
-        <v>51</v>
-      </c>
-      <c r="F33" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>99</v>
+      </c>
+      <c r="F35" t="s">
         <v>100</v>
-      </c>
-      <c r="B35" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" t="s">
-        <v>101</v>
-      </c>
-      <c r="F35" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" t="s">
         <v>103</v>
-      </c>
-      <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F36" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" t="s">
+        <v>105</v>
+      </c>
+      <c r="E37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" t="s">
         <v>106</v>
-      </c>
-      <c r="B37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" t="s">
-        <v>107</v>
-      </c>
-      <c r="E37" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
         <v>109</v>
-      </c>
-      <c r="B38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" t="s">
         <v>112</v>
-      </c>
-      <c r="B39" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" t="s">
-        <v>25</v>
-      </c>
-      <c r="D39" t="s">
-        <v>113</v>
-      </c>
-      <c r="F39" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" t="s">
         <v>115</v>
-      </c>
-      <c r="B40" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" t="s">
-        <v>51</v>
-      </c>
-      <c r="F40" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="s">
         <v>118</v>
-      </c>
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" t="s">
-        <v>31</v>
-      </c>
-      <c r="D41" t="s">
-        <v>119</v>
-      </c>
-      <c r="E41" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" t="s">
         <v>121</v>
       </c>
-      <c r="B42" t="s">
+      <c r="D42" t="s">
         <v>122</v>
       </c>
-      <c r="C42" t="s">
+      <c r="F42" t="s">
         <v>123</v>
-      </c>
-      <c r="D42" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F43" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>128</v>
+      </c>
+      <c r="F44" t="s">
         <v>129</v>
-      </c>
-      <c r="B44" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" t="s">
-        <v>130</v>
-      </c>
-      <c r="F44" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>131</v>
+      </c>
+      <c r="F45" t="s">
         <v>132</v>
-      </c>
-      <c r="B45" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" t="s">
-        <v>133</v>
-      </c>
-      <c r="F45" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" t="s">
+        <v>134</v>
+      </c>
+      <c r="F46" t="s">
         <v>135</v>
-      </c>
-      <c r="B46" t="s">
-        <v>122</v>
-      </c>
-      <c r="C46" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" t="s">
-        <v>136</v>
-      </c>
-      <c r="F46" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" t="s">
+        <v>120</v>
+      </c>
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s">
+        <v>137</v>
+      </c>
+      <c r="F47" t="s">
         <v>138</v>
-      </c>
-      <c r="B47" t="s">
-        <v>122</v>
-      </c>
-      <c r="C47" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" t="s">
-        <v>139</v>
-      </c>
-      <c r="F47" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F48" t="s">
         <v>141</v>
-      </c>
-      <c r="B48" t="s">
-        <v>122</v>
-      </c>
-      <c r="C48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D48" t="s">
-        <v>142</v>
-      </c>
-      <c r="F48" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
+        <v>143</v>
+      </c>
+      <c r="E49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F49" t="s">
         <v>144</v>
-      </c>
-      <c r="B49" t="s">
-        <v>122</v>
-      </c>
-      <c r="C49" t="s">
-        <v>31</v>
-      </c>
-      <c r="D49" t="s">
-        <v>145</v>
-      </c>
-      <c r="E49" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" t="s">
         <v>151</v>
-      </c>
-      <c r="B51" t="s">
-        <v>148</v>
-      </c>
-      <c r="C51" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" t="s">
-        <v>152</v>
-      </c>
-      <c r="F51" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>153</v>
+      </c>
+      <c r="F52" t="s">
         <v>154</v>
-      </c>
-      <c r="B52" t="s">
-        <v>148</v>
-      </c>
-      <c r="C52" t="s">
-        <v>16</v>
-      </c>
-      <c r="D52" t="s">
-        <v>155</v>
-      </c>
-      <c r="F52" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" t="s">
+        <v>146</v>
+      </c>
+      <c r="C53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" t="s">
+        <v>156</v>
+      </c>
+      <c r="F53" t="s">
         <v>157</v>
-      </c>
-      <c r="B53" t="s">
-        <v>148</v>
-      </c>
-      <c r="C53" t="s">
-        <v>19</v>
-      </c>
-      <c r="D53" t="s">
-        <v>158</v>
-      </c>
-      <c r="F53" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>158</v>
+      </c>
+      <c r="B54" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" t="s">
+        <v>159</v>
+      </c>
+      <c r="F54" t="s">
         <v>160</v>
-      </c>
-      <c r="B54" t="s">
-        <v>148</v>
-      </c>
-      <c r="C54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" t="s">
-        <v>161</v>
-      </c>
-      <c r="F54" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" t="s">
+        <v>146</v>
+      </c>
+      <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>162</v>
+      </c>
+      <c r="F55" t="s">
         <v>163</v>
-      </c>
-      <c r="B55" t="s">
-        <v>148</v>
-      </c>
-      <c r="C55" t="s">
-        <v>25</v>
-      </c>
-      <c r="D55" t="s">
-        <v>164</v>
-      </c>
-      <c r="F55" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" t="s">
+        <v>146</v>
+      </c>
+      <c r="C56" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" t="s">
+        <v>165</v>
+      </c>
+      <c r="E56" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" t="s">
         <v>166</v>
-      </c>
-      <c r="B56" t="s">
-        <v>148</v>
-      </c>
-      <c r="C56" t="s">
-        <v>28</v>
-      </c>
-      <c r="D56" t="s">
-        <v>167</v>
-      </c>
-      <c r="E56" t="s">
-        <v>51</v>
-      </c>
-      <c r="F56" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" t="s">
+        <v>146</v>
+      </c>
+      <c r="C57" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57" t="s">
+        <v>168</v>
+      </c>
+      <c r="E57" t="s">
+        <v>49</v>
+      </c>
+      <c r="F57" t="s">
         <v>169</v>
-      </c>
-      <c r="B57" t="s">
-        <v>148</v>
-      </c>
-      <c r="C57" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" t="s">
-        <v>170</v>
-      </c>
-      <c r="E57" t="s">
-        <v>51</v>
-      </c>
-      <c r="F57" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" t="s">
         <v>172</v>
       </c>
-      <c r="B58" t="s">
+      <c r="D58" t="s">
         <v>173</v>
       </c>
-      <c r="C58" t="s">
+      <c r="F58" t="s">
         <v>174</v>
-      </c>
-      <c r="D58" t="s">
-        <v>175</v>
-      </c>
-      <c r="F58" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" t="s">
+        <v>172</v>
+      </c>
+      <c r="D59" t="s">
         <v>177</v>
       </c>
-      <c r="B59" t="s">
+      <c r="F59" t="s">
         <v>178</v>
-      </c>
-      <c r="C59" t="s">
-        <v>174</v>
-      </c>
-      <c r="D59" t="s">
-        <v>179</v>
-      </c>
-      <c r="F59" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" t="s">
+        <v>172</v>
+      </c>
+      <c r="D60" t="s">
         <v>181</v>
       </c>
-      <c r="B60" t="s">
+      <c r="F60" t="s">
         <v>182</v>
-      </c>
-      <c r="C60" t="s">
-        <v>174</v>
-      </c>
-      <c r="D60" t="s">
-        <v>183</v>
-      </c>
-      <c r="F60" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" t="s">
+        <v>184</v>
+      </c>
+      <c r="C61" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" t="s">
         <v>185</v>
       </c>
-      <c r="B61" t="s">
+      <c r="F61" t="s">
         <v>186</v>
-      </c>
-      <c r="C61" t="s">
-        <v>174</v>
-      </c>
-      <c r="D61" t="s">
-        <v>187</v>
-      </c>
-      <c r="F61" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>187</v>
+      </c>
+      <c r="B62" t="s">
+        <v>188</v>
+      </c>
+      <c r="C62" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62" t="s">
         <v>189</v>
       </c>
-      <c r="B62" t="s">
+      <c r="E62" t="s">
         <v>190</v>
       </c>
-      <c r="C62" t="s">
-        <v>174</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="F62" t="s">
         <v>191</v>
-      </c>
-      <c r="E62" t="s">
-        <v>192</v>
-      </c>
-      <c r="F62" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>192</v>
+      </c>
+      <c r="B63" t="s">
+        <v>193</v>
+      </c>
+      <c r="C63" t="s">
+        <v>172</v>
+      </c>
+      <c r="D63" t="s">
         <v>194</v>
       </c>
-      <c r="B63" t="s">
+      <c r="F63" t="s">
         <v>195</v>
-      </c>
-      <c r="C63" t="s">
-        <v>174</v>
-      </c>
-      <c r="D63" t="s">
-        <v>196</v>
-      </c>
-      <c r="F63" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>196</v>
+      </c>
+      <c r="B64" t="s">
+        <v>197</v>
+      </c>
+      <c r="C64" t="s">
+        <v>172</v>
+      </c>
+      <c r="D64" t="s">
         <v>198</v>
       </c>
-      <c r="B64" t="s">
+      <c r="F64" t="s">
         <v>199</v>
-      </c>
-      <c r="C64" t="s">
-        <v>174</v>
-      </c>
-      <c r="D64" t="s">
-        <v>200</v>
-      </c>
-      <c r="F64" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>200</v>
+      </c>
+      <c r="B65" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" t="s">
+        <v>201</v>
+      </c>
+      <c r="E65" t="s">
+        <v>49</v>
+      </c>
+      <c r="F65" t="s">
         <v>202</v>
-      </c>
-      <c r="B65" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" t="s">
-        <v>28</v>
-      </c>
-      <c r="D65" t="s">
-        <v>203</v>
-      </c>
-      <c r="E65" t="s">
-        <v>51</v>
-      </c>
-      <c r="F65" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>203</v>
+      </c>
+      <c r="B66" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" t="s">
+        <v>30</v>
+      </c>
+      <c r="D66" t="s">
+        <v>204</v>
+      </c>
+      <c r="E66" t="s">
+        <v>49</v>
+      </c>
+      <c r="F66" t="s">
         <v>205</v>
-      </c>
-      <c r="B66" t="s">
-        <v>122</v>
-      </c>
-      <c r="C66" t="s">
-        <v>31</v>
-      </c>
-      <c r="D66" t="s">
-        <v>206</v>
-      </c>
-      <c r="E66" t="s">
-        <v>51</v>
-      </c>
-      <c r="F66" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>206</v>
+      </c>
+      <c r="B67" t="s">
+        <v>207</v>
+      </c>
+      <c r="C67" t="s">
+        <v>172</v>
+      </c>
+      <c r="D67" t="s">
         <v>208</v>
       </c>
-      <c r="B67" t="s">
+      <c r="F67" t="s">
         <v>209</v>
-      </c>
-      <c r="C67" t="s">
-        <v>174</v>
-      </c>
-      <c r="D67" t="s">
-        <v>210</v>
-      </c>
-      <c r="F67" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C68" t="s">
         <v>8</v>
       </c>
       <c r="D68" t="s">
+        <v>212</v>
+      </c>
+      <c r="E68" t="s">
+        <v>213</v>
+      </c>
+      <c r="F68" t="s">
         <v>214</v>
-      </c>
-      <c r="E68" t="s">
-        <v>215</v>
-      </c>
-      <c r="F68" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>215</v>
+      </c>
+      <c r="B69" t="s">
+        <v>211</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" t="s">
+        <v>216</v>
+      </c>
+      <c r="E69" t="s">
+        <v>213</v>
+      </c>
+      <c r="F69" t="s">
         <v>217</v>
-      </c>
-      <c r="B69" t="s">
-        <v>213</v>
-      </c>
-      <c r="C69" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" t="s">
-        <v>218</v>
-      </c>
-      <c r="E69" t="s">
-        <v>215</v>
-      </c>
-      <c r="F69" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>218</v>
+      </c>
+      <c r="B70" t="s">
+        <v>211</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>219</v>
+      </c>
+      <c r="E70" t="s">
+        <v>213</v>
+      </c>
+      <c r="F70" t="s">
         <v>220</v>
-      </c>
-      <c r="B70" t="s">
-        <v>213</v>
-      </c>
-      <c r="C70" t="s">
-        <v>16</v>
-      </c>
-      <c r="D70" t="s">
-        <v>221</v>
-      </c>
-      <c r="E70" t="s">
-        <v>215</v>
-      </c>
-      <c r="F70" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B71" t="s">
+        <v>211</v>
+      </c>
+      <c r="C71" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" t="s">
+        <v>222</v>
+      </c>
+      <c r="E71" t="s">
         <v>213</v>
       </c>
-      <c r="C71" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" t="s">
-        <v>224</v>
-      </c>
-      <c r="E71" t="s">
-        <v>215</v>
-      </c>
       <c r="F71" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B72" t="s">
+        <v>211</v>
+      </c>
+      <c r="C72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" t="s">
+        <v>224</v>
+      </c>
+      <c r="E72" t="s">
         <v>213</v>
       </c>
-      <c r="C72" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" t="s">
-        <v>226</v>
-      </c>
-      <c r="E72" t="s">
-        <v>215</v>
-      </c>
       <c r="F72" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>225</v>
+      </c>
+      <c r="B73" t="s">
+        <v>211</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" t="s">
+        <v>226</v>
+      </c>
+      <c r="E73" t="s">
+        <v>213</v>
+      </c>
+      <c r="F73" t="s">
         <v>227</v>
-      </c>
-      <c r="B73" t="s">
-        <v>213</v>
-      </c>
-      <c r="C73" t="s">
-        <v>25</v>
-      </c>
-      <c r="D73" t="s">
-        <v>228</v>
-      </c>
-      <c r="E73" t="s">
-        <v>215</v>
-      </c>
-      <c r="F73" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>228</v>
+      </c>
+      <c r="B74" t="s">
+        <v>211</v>
+      </c>
+      <c r="C74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74" t="s">
+        <v>229</v>
+      </c>
+      <c r="E74" t="s">
+        <v>213</v>
+      </c>
+      <c r="F74" t="s">
         <v>230</v>
-      </c>
-      <c r="B74" t="s">
-        <v>213</v>
-      </c>
-      <c r="C74" t="s">
-        <v>28</v>
-      </c>
-      <c r="D74" t="s">
-        <v>231</v>
-      </c>
-      <c r="E74" t="s">
-        <v>215</v>
-      </c>
-      <c r="F74" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B75" t="s">
+        <v>211</v>
+      </c>
+      <c r="C75" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" t="s">
+        <v>232</v>
+      </c>
+      <c r="E75" t="s">
         <v>213</v>
       </c>
-      <c r="C75" t="s">
-        <v>31</v>
-      </c>
-      <c r="D75" t="s">
-        <v>234</v>
-      </c>
-      <c r="E75" t="s">
-        <v>215</v>
-      </c>
       <c r="F75" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B76" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C76" t="s">
         <v>8</v>
       </c>
       <c r="D76" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>236</v>
+      </c>
+      <c r="B77" t="s">
+        <v>234</v>
+      </c>
+      <c r="C77" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" t="s">
+        <v>237</v>
+      </c>
+      <c r="F77" t="s">
         <v>238</v>
-      </c>
-      <c r="B77" t="s">
-        <v>236</v>
-      </c>
-      <c r="C77" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" t="s">
-        <v>239</v>
-      </c>
-      <c r="F77" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>239</v>
+      </c>
+      <c r="B78" t="s">
+        <v>234</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s">
+        <v>240</v>
+      </c>
+      <c r="F78" t="s">
         <v>241</v>
-      </c>
-      <c r="B78" t="s">
-        <v>236</v>
-      </c>
-      <c r="C78" t="s">
-        <v>16</v>
-      </c>
-      <c r="D78" t="s">
-        <v>242</v>
-      </c>
-      <c r="F78" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>242</v>
+      </c>
+      <c r="B79" t="s">
+        <v>234</v>
+      </c>
+      <c r="C79" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" t="s">
+        <v>243</v>
+      </c>
+      <c r="F79" t="s">
         <v>244</v>
-      </c>
-      <c r="B79" t="s">
-        <v>236</v>
-      </c>
-      <c r="C79" t="s">
-        <v>19</v>
-      </c>
-      <c r="D79" t="s">
-        <v>245</v>
-      </c>
-      <c r="F79" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>245</v>
+      </c>
+      <c r="B80" t="s">
+        <v>234</v>
+      </c>
+      <c r="C80" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" t="s">
+        <v>246</v>
+      </c>
+      <c r="F80" t="s">
         <v>247</v>
-      </c>
-      <c r="B80" t="s">
-        <v>236</v>
-      </c>
-      <c r="C80" t="s">
-        <v>22</v>
-      </c>
-      <c r="D80" t="s">
-        <v>248</v>
-      </c>
-      <c r="F80" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>248</v>
+      </c>
+      <c r="B81" t="s">
+        <v>234</v>
+      </c>
+      <c r="C81" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" t="s">
+        <v>249</v>
+      </c>
+      <c r="F81" t="s">
         <v>250</v>
-      </c>
-      <c r="B81" t="s">
-        <v>236</v>
-      </c>
-      <c r="C81" t="s">
-        <v>25</v>
-      </c>
-      <c r="D81" t="s">
-        <v>251</v>
-      </c>
-      <c r="F81" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>251</v>
+      </c>
+      <c r="B82" t="s">
+        <v>234</v>
+      </c>
+      <c r="C82" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82" t="s">
+        <v>252</v>
+      </c>
+      <c r="F82" t="s">
         <v>253</v>
-      </c>
-      <c r="B82" t="s">
-        <v>236</v>
-      </c>
-      <c r="C82" t="s">
-        <v>31</v>
-      </c>
-      <c r="D82" t="s">
-        <v>254</v>
-      </c>
-      <c r="F82" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>254</v>
+      </c>
+      <c r="B83" t="s">
+        <v>255</v>
+      </c>
+      <c r="C83" t="s">
+        <v>172</v>
+      </c>
+      <c r="D83" t="s">
         <v>256</v>
       </c>
-      <c r="B83" t="s">
+      <c r="F83" t="s">
         <v>257</v>
-      </c>
-      <c r="C83" t="s">
-        <v>174</v>
-      </c>
-      <c r="D83" t="s">
-        <v>258</v>
-      </c>
-      <c r="F83" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>258</v>
+      </c>
+      <c r="B84" t="s">
+        <v>259</v>
+      </c>
+      <c r="C84" t="s">
+        <v>172</v>
+      </c>
+      <c r="D84" t="s">
         <v>260</v>
       </c>
-      <c r="B84" t="s">
+      <c r="F84" t="s">
         <v>261</v>
-      </c>
-      <c r="C84" t="s">
-        <v>174</v>
-      </c>
-      <c r="D84" t="s">
-        <v>262</v>
-      </c>
-      <c r="F84" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>262</v>
+      </c>
+      <c r="B85" t="s">
+        <v>259</v>
+      </c>
+      <c r="C85" t="s">
+        <v>172</v>
+      </c>
+      <c r="D85" t="s">
+        <v>263</v>
+      </c>
+      <c r="F85" t="s">
         <v>264</v>
-      </c>
-      <c r="B85" t="s">
-        <v>261</v>
-      </c>
-      <c r="C85" t="s">
-        <v>174</v>
-      </c>
-      <c r="D85" t="s">
-        <v>265</v>
-      </c>
-      <c r="F85" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>265</v>
+      </c>
+      <c r="B86" t="s">
+        <v>259</v>
+      </c>
+      <c r="C86" t="s">
+        <v>172</v>
+      </c>
+      <c r="D86" t="s">
+        <v>266</v>
+      </c>
+      <c r="F86" t="s">
         <v>267</v>
-      </c>
-      <c r="B86" t="s">
-        <v>261</v>
-      </c>
-      <c r="C86" t="s">
-        <v>174</v>
-      </c>
-      <c r="D86" t="s">
-        <v>268</v>
-      </c>
-      <c r="F86" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>268</v>
+      </c>
+      <c r="B87" t="s">
+        <v>259</v>
+      </c>
+      <c r="C87" t="s">
+        <v>172</v>
+      </c>
+      <c r="D87" t="s">
+        <v>269</v>
+      </c>
+      <c r="F87" t="s">
         <v>270</v>
-      </c>
-      <c r="B87" t="s">
-        <v>261</v>
-      </c>
-      <c r="C87" t="s">
-        <v>174</v>
-      </c>
-      <c r="D87" t="s">
-        <v>271</v>
-      </c>
-      <c r="F87" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>271</v>
+      </c>
+      <c r="B88" t="s">
+        <v>259</v>
+      </c>
+      <c r="C88" t="s">
+        <v>172</v>
+      </c>
+      <c r="D88" t="s">
+        <v>272</v>
+      </c>
+      <c r="F88" t="s">
         <v>273</v>
-      </c>
-      <c r="B88" t="s">
-        <v>261</v>
-      </c>
-      <c r="C88" t="s">
-        <v>174</v>
-      </c>
-      <c r="D88" t="s">
-        <v>274</v>
-      </c>
-      <c r="F88" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>274</v>
+      </c>
+      <c r="B89" t="s">
+        <v>259</v>
+      </c>
+      <c r="C89" t="s">
+        <v>172</v>
+      </c>
+      <c r="D89" t="s">
+        <v>275</v>
+      </c>
+      <c r="F89" t="s">
         <v>276</v>
-      </c>
-      <c r="B89" t="s">
-        <v>261</v>
-      </c>
-      <c r="C89" t="s">
-        <v>174</v>
-      </c>
-      <c r="D89" t="s">
-        <v>277</v>
-      </c>
-      <c r="F89" t="s">
-        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF50044-1501-4CBA-B8FE-665D46FD123C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB95140-047E-4D28-9DA3-3FC75AF0F5F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -817,14 +817,6 @@
     <t>등록금, 수강료, 추가 등록금, 학비, 납부, 추가등록금, 감면, 면제, 장학금, 환불, 고지, 등록금고지, 고지서, 학비얼마, 비용얼마, 추가비용, 추가학비, 더내야하나, 등록금추가, 등록금더, 등록금별도, 돈얼마, 비용</t>
   </si>
   <si>
-    <t>💰 등록금 안내
-▸ 원전공 기준의 등록금을 납부하면 됨
-▸ 다전공을 신청해도 추가 등록금 없음!
-▸ 다전공 제도 참여 시 별도 장학금 지원은 현재 없음
-💡 등록금 고지, 환불 등은 학교 홈페이지 참조: https://www.hknu.ac.kr/bbs/kor/69/94055/artclView.do?layout=unknown
-📞 재무팀: 031-670-5476</t>
-  </si>
-  <si>
     <t>F058</t>
   </si>
   <si>
@@ -834,13 +826,6 @@
     <t>졸업식, 졸업식은, 졸업식은언제, 학위수여식은, 학위수여식은언제, 졸업, 학위수여, 졸업일정, 졸업날짜, 졸업시기, 학위받는날, 언제졸업, 졸업하는날</t>
   </si>
   <si>
-    <t>🎓 졸업식 일정
-▸ 전기 졸업식: 매년 2월 중순
-▸ 후기 졸업식: 매년 8월 중순
-💡 정확한 일정은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/92840/artclView.do?layout=unknown
-📞 학사지원팀: 031-670-5036</t>
-  </si>
-  <si>
     <t>F059</t>
   </si>
   <si>
@@ -850,20 +835,6 @@
     <t>증명서, 증명서발급, 졸업증명서, 재학증명서, 수료증명서, 전과, 전공변경, 휴학, 복학, 재입학, 서류, 서류발급, 문서, 증명, 발급방법, 어떻게발급, 이수증명, 영문증명서, 국문증명서</t>
   </si>
   <si>
-    <t>📄 증명서 발급 안내
-📌 발급 가능 증명서:
-▸ 재학증명서, 졸업증명서, 성적증명서, 수료증명서 등
-▸ 국문/영문 모두 발급 가능
-💻 온라인 발급:
-▸ 정부24(https://www.gov.kr)에서 발급 가능
-▸ 써트피아(https://certpia.com)에서 발급 가능
-🏢 오프라인 발급:
-▸ 본관 1층 무인발급기 이용
-📌 전과(전공변경), 휴복학, 재입학 등도 학사지원팀에서 처리
-💡 학사공지 참조: https://www.hknu.ac.kr/kor/562/subview.do
-📞 학사지원팀: 031-670-5037</t>
-  </si>
-  <si>
     <t>F060</t>
   </si>
   <si>
@@ -873,20 +844,6 @@
     <t>학점교류, 학점인정, 이수구분, 계절학기, 타대학, 타교, 다른학교, 학점인정방법, 학점인정되나, 인정받나, 교환학생, 교류학점, 타교학점, 계절학기신청, 계절학기는, 여름학기, 겨울학기</t>
   </si>
   <si>
-    <t>🔄 학점교류 안내
-📌 학점교류란?
-▸ 국내외 대학에서 이수한 학점을 본교 학점으로 인정받는 제도
-📋 종류:
-▸ 국내외 대학 학점교류 (협약 대학 간)
-▸ 계절학기 (여름/겨울 방학 중 타교 수강)
-📌 유의사항:
-▸ 사전에 학점인정 신청 필요
-▸ 이수구분(전필, 전선, 교양 등) 확인 후 신청
-▸ 학과 및 학사지원팀 승인 필요
-💡 학사공지 참조: https://www.hknu.ac.kr/kor/562/subview.do
-📞 학사지원팀: 031-670-5034</t>
-  </si>
-  <si>
     <t>F061</t>
   </si>
   <si>
@@ -899,21 +856,6 @@
     <t>계절학기, 여름학기, 겨울학기</t>
   </si>
   <si>
-    <t>📝 수강 관련 안내
-📌 수강신청:
-▸ 매 학기 개강 전 수강신청 기간에 학사시스템에서 신청
-▸ 수강신청 정정기간에 과목 변경 가능
-📌 수강철회:
-▸ 학기 중 수강철회 기간에 신청 가능
-▸ 철회한 과목은 성적표에 'W'로 표기
-▸ 재수강과 다름 (재수강은 이전 성적 대체)
-📌 성적 이의신청:
-▸ 성적 공시 후 정정기간 내 신청
-▸ 성적확인: 학사시스템(https://info.hknu.ac.kr)에서 조회
-💡 학사공지 참조: https://www.hknu.ac.kr/kor/562/subview.do
-📞 학사지원팀: 031-670-5032</t>
-  </si>
-  <si>
     <t>F062</t>
   </si>
   <si>
@@ -923,22 +865,6 @@
     <t>교직, 교직이수, 교원자격, 교원자격증, 교직과정, 자유학기, 자유학기제, 교사자격증, 교직이수방법, 교직신청, 교직과정신청, 자유학기제교직, 교직학점</t>
   </si>
   <si>
-    <t>👨‍🏫 교직 이수 안내
-📌 교직과정이란?
-▸ 소정의 교직과목을 이수하여 교원자격증(2급 정교사)을 취득하는 과정
-📋 신청 자격:
-▸ 교직과정 설치 학과 학생만 신청 가능
-▸ 학과별 선발인원 제한 있음
-📌 이수 조건:
-▸ 전공과목 + 교직과목 + 교육실습 이수 필요
-📌 유의사항:
-▸ 교직 적성·인성검사 통과 필요
-▸ 응급처치 실습 이수 필요
-▸ 성적 기준 충족 필요 (전공/교직 평균 일정 이상)
-💡 학사공지 참조: https://www.hknu.ac.kr/kor/562/subview.do
-📞 학사지원팀: 031-670-5036</t>
-  </si>
-  <si>
     <t>F063</t>
   </si>
   <si>
@@ -946,15 +872,6 @@
   </si>
   <si>
     <t>졸업유예, 졸업유예시기, 졸업유예언제, 조기졸업, 조기졸업시기, 조기졸업언제, 유예, 유예시기, 유예언제, 졸업늦추, 졸업미루, 졸업연기, 조기, 빨리졸업, 일찍졸업, 유예신청, 유예방법, 유예기간, 조기졸업조건, 조기졸업방법, 언제까지유예</t>
-  </si>
-  <si>
-    <t>⏰ 졸업유예/조기졸업 안내
-📅 접수 시기:
-▸ 2월 졸업: 1월에 접수
-▸ 8월 졸업: 7월에 접수
-💡 졸업유예: https://www.hknu.ac.kr/bbs/kor/70/91130/artclView.do?layout=unknown
-💡 조기졸업: https://www.hknu.ac.kr/bbs/kor/70/91129/artclView.do?layout=unknown
-📞 학사지원팀: 031-670-5036</t>
   </si>
   <si>
     <t>F064</t>
@@ -1014,12 +931,6 @@
     <t>성적확인, 성적확인하려, 성적확인하고싶, 성적확인하고, 성적확인하려, 이수학점확인, 내성적확인, 내성적확인하고싶, 수강신청확인, 수강신청확인하고싶, 수강신청내역확인하려, 수강신청내역, 내수강신청확인, 성적조회, 성적조회하려, 성적보기, 성적어떻게봐, 성적어디서봐, 성적어디서확인, 내성적조회, 내성적보기, 학점확인, 학점조회, 내학점확인, 내학점조회, 이수학점조회, 총이수학점확인, 총이수학점조회, 취득학점확인, 취득학점조회, 들은학점확인, 이수한학점확인, 내이수학점확인, 내이수학점조회, 수강내역확인, 수강내역조회, 수강과목확인, 수강과목조회, 들은과목확인, 수강확인, 수강조회, 내수강내역확인, 내수강과목확인, 수강신청내역조회, 어떤과목들었, 무슨과목들었는지</t>
   </si>
   <si>
-    <t>📊 성적/수강 확인 안내
-성적확인, 이수학점 확인, 수강조회 등
-💻 학사시스템에서 확인: https://info.hknu.ac.kr
-📞 학사지원팀: 031-670-5032</t>
-  </si>
-  <si>
     <t>F067</t>
   </si>
   <si>
@@ -1208,11 +1119,6 @@
     <t>개강, 개강일, 종강, 종강일, 방학, 여름방학, 겨울방학, 학사일정, 학기시작, 학기일정, 수업시작, 수업종료, 기말고사, 중간고사, 시험기간, 학기언제, 개강언제, 종강언제, 방학언제, 몇월개강, 1학기, 2학기시작, 학사달력, 학년도일정</t>
   </si>
   <si>
-    <t>📅 학사일정(개강일, 종강일, 시험기간, 방학 등)은 학교 홈페이지에서 확인하세요.
-🔗 학사일정 바로가기: https://www.hknu.ac.kr/kor/646/subview.do
-💡 이 챗봇은 다전공·유연학사 제도 전용입니다. 학사일정 관련 자세한 문의는 학사지원팀(031-670-5032)으로 연락해 주세요.</t>
-  </si>
-  <si>
     <t>F083</t>
   </si>
   <si>
@@ -1222,78 +1128,34 @@
     <t>강의개설,시간표편성,시간표,강의계획서,수강신청,수강신청변경,수강변경,교과목설폐강,설폐강,수강철회,강의개설문의,수강신청문의,수강철회문의,시간표문의</t>
   </si>
   <si>
-    <t>📞 해당 업무의 담당 연락처를 안내해 드릴게요!
-▶ 강의개설 및 시간표 편성, 강의계획서, 수강신청, 수강신청변경, 교과목 설·폐강, 수강철회 관련 문의
-☎ 031-670-5032
-💡 평일 근무시간(09:00~18:00)에 연락해 주세요.</t>
-  </si>
-  <si>
     <t>F084</t>
   </si>
   <si>
     <t>성적입력,성적열람,성적정정,성적확정,학사경고,제적처리,성적문의,성적입력문의,학사경고문의,제적문의</t>
   </si>
   <si>
-    <t>📞 해당 업무의 담당 연락처를 안내해 드릴게요!
-▶ 성적입력 및 열람, 성적 정정, 성적 확정, 학사경고 및 제적처리 관련 문의
-☎ 031-670-5032
-💡 평일 근무시간(09:00~18:00)에 연락해 주세요.</t>
-  </si>
-  <si>
     <t>F085</t>
   </si>
   <si>
     <t>전과,재입학,전공배정,출석인정,학적변동,휴학,복학,제적,증명서,제증명,졸업증명서,성적증명서,학적변동문의,전과문의,재입학문의,휴학문의,복학문의</t>
   </si>
   <si>
-    <t>📞 해당 업무의 담당 연락처를 안내해 드릴게요!
-▶ 전과 및 재입학, 전공배정, 출석인정, 학적변동(휴·복학, 제적 등), 성적·졸업증명서 등 각종 제증명 관련 문의
-☎ 031-670-5033
-💡 평일 근무시간(09:00~18:00)에 연락해 주세요.</t>
-  </si>
-  <si>
     <t>F086</t>
   </si>
   <si>
     <t>계절수업,계절학기,이수구분변경,이수구분,대체과목,유사과목,성적삭제,학점교류,군복무,OCU,군복무학점,취득학점인정,계절수업문의,학점교류문의</t>
   </si>
   <si>
-    <t>📞 해당 업무의 담당 연락처를 안내해 드릴게요!
-▶ 계절수업, 이수구분 변경, 대체·유사과목 성적 삭제, 학점교류, 군복무중 취득학점 인정(OCU) 관련 문의
-☎ 031-670-5034
-💡 평일 근무시간(09:00~18:00)에 연락해 주세요.</t>
-  </si>
-  <si>
     <t>F087</t>
   </si>
   <si>
     <t>교직과정,교직,교원자격증,교원자격,강의평가,SWAN,스완,특별학기,자유학기,학위수여,학위수여식,졸업식,온라인학위,온라인학위과정,복수학위,공동학위,시간제등록생,시간제,교직문의,학위수여문의,강의평가문의</t>
   </si>
   <si>
-    <t>📞 해당 업무의 담당 연락처를 안내해 드릴게요!
-▶ 교직과정, 교원자격증, 강의평가, SWAN, 특별학기, 자유학기, 학위수여, 학위수여식, 온라인 학위과정, 복수학위 및 공동학위, 시간제 등록생 관련 문의
-☎ 031-670-5036
-💡 평일 근무시간(09:00~18:00)에 연락해 주세요.</t>
-  </si>
-  <si>
     <t>F088</t>
   </si>
   <si>
     <t>학사지원팀,학사지원팀연락처,학사지원팀전화번호,학사제도문의,학사업무문의,학사업무연락처,학사지원팀문의처,학사제도연락처,학사제도전화번호</t>
-  </si>
-  <si>
-    <t>📞 학사지원팀 업무별 연락처를 안내해 드릴게요!
-▶ 강의개설 및 시간표 편성, 강의계획서, 수강신청, 수강신청변경, 교과목 설·폐강, 수강철회
-☎ 031-670-5032
-▶ 성적입력 및 열람, 성적 정정, 성적 확정, 학사경고 및 제적처리
-☎ 031-670-5032
-▶ 전과 및 재입학, 전공배정, 출석인정, 학적변동(휴·복학, 제적 등), 성적·졸업증명서 등 각종 제증명
-☎ 031-670-5033
-▶ 계절수업, 이수구분 변경, 대체·유사과목 성적 삭제, 학점교류, 군복무중 취득학점 인정(OCU)
-☎ 031-670-5034
-▶ 교직과정, 교원자격증, 강의평가, SWAN, 특별학기, 자유학기, 학위수여, 학위수여식, 온라인 학위과정, 복수학위 및 공동학위, 시간제 등록생
-☎ 031-670-5036
-💡 평일 근무시간(09:00~18:00)에 연락해 주세요.</t>
   </si>
   <si>
     <r>
@@ -1579,12 +1441,3128 @@
 💡 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사일정(개강일, 종강일, 시험기간, 방학 등)은 학교 홈페이지에서 확인하세요.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사일정 바로가기: https://www.hknu.ac.kr/kor/646/subview.do
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이 챗봇은 유연학사제도(다전공) 전용입니다. 학사일정 관련 자세한 문의는 학사지원팀(031-670-5032)으로 연락해 주세요.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업유예/조기졸업 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 접수 시기:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2월 졸업: 1월에 접수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 8월 졸업: 7월에 접수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업유예 참고: https://www.hknu.ac.kr/bbs/kor/70/91130/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 조기졸업 참고: https://www.hknu.ac.kr/bbs/kor/70/91129/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5035</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 강의개설 및 시간표 편성, 강의계획서, 수강신청, 수강신청변경, 교과목 설·폐강, 수강철회 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사지원팀 031-670-5032
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> * 점심시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(12:00~13:00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 제외</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적입력 및 열람, 성적 정정, 성적 확정, 학사경고 및 제적처리 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사지원팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">031-670-5032
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>근무시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(09:00~18:00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>연락해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>점심시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(12:00~13:00) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 계절수업, 이수구분 변경, 대체·유사과목 성적 삭제, 학점교류, 군복무중 취득학점 인정(OCU) 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사지원팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">031-670-5034
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>근무시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(09:00~18:00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>연락해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>점심시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(12:00~13:00) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교직과정, 교원자격증, 강의평가, SWAN, 특별학기, 자유학기, 학위수여, 학위수여식, 온라인 학위과정, 복수학위 및 공동학위, 시간제 등록생 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사지원팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">031-670-5036
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>근무시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(09:00~18:00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>연락해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>점심시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(12:00~13:00) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사지원팀 업무별 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 강의개설 및 시간표 편성, 강의계획서, 수강신청, 수강신청변경, 교과목 설·폐강, 수강철회
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사지원팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">031-670-5032
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적입력 및 열람, 성적 정정, 성적 확정, 학사경고 및 제적처리
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 031-670-5032
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전과 및 재입학, 전공배정, 출석인정, 학적변동(휴·복학, 제적 등), 성적·졸업증명서 등 각종 제증명
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 031-670-5033
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 계절수업, 이수구분 변경, 대체·유사과목 성적 삭제, 학점교류, 군복무중 취득학점 인정(OCU)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 031-670-5034
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교직과정, 교원자격증, 강의평가, SWAN, 특별학기, 자유학기, 학위수여, 학위수여식, 온라인 학위과정, 복수학위 및 공동학위, 시간제 등록생
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 031-670-5036
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>근무시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(09:00~18:00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>연락해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>점심시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(12:00~13:00) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전과 및 재입학, 전공배정, 출석인정, 학적변동(휴·복학, 제적 등), 성적·졸업증명서 등 각종 제증명 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사지원팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">031-670-5037
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>근무시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(09:00~18:00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>연락해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>점심시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(12:00~13:00) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적/수강 확인 안내
+성적확인, 이수학점 확인, 수강조회 등
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사시스템에서 확인: https://info.hknu.ac.kr
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5032</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>👨‍🏫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교직 이수 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교직과정이란?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 소정의 교직과목을 이수하여 교원자격증(2급 정교사)을 취득하는 과정
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 자격:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교직과정 설치 학과 학생만 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학과별 선발인원 제한 있음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수 조건:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전공과목 + 교직과목 + 교육실습 이수 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유의사항:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 교직 적성·인성검사 통과 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 응급처치 실습 이수 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적 기준 충족 필요 (전공/교직 평균 일정 이상)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지 참조: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>https://www.hknu.ac.kr/bbs/kor/70/92919/artclView.do?layout=unknown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5036</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 관련 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 수강신청:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 매 학기 개강 전 수강신청 기간에 수강신청 시스템(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>http://sugang.hknu.ac.kr)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 신청
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 수강신청 정정기간에 과목 변경 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 수강철회:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학기 중 수강철회 기간에 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 재수강과 다름 (재수강은 이전 성적 대체)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적 이의신청:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적 공시 후 정정기간 내 신청
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적확인: 학사시스템(https://info.hknu.ac.kr)에서 조회
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지 참조: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>https://www.hknu.ac.kr/bbs/kor/70/91760/artclView.do?layout=unknown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5032</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학점교류 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학점교류란?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 국내외 대학에서 이수한 학점을 본교 학점으로 인정받는 제도
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 종류:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 국내외 대학 학점교류 (협약 대학 간)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 계절학기 (여름/겨울 방학 중 타교 수강)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유의사항:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 사전에 학점인정 신청 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수구분(전필, 전선, 교양 등) 확인 후 신청
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전공 및 학사지원팀 승인 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지 참조: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>https://www.hknu.ac.kr/bbs/kor/70/92201/artclView.do?layout=unknown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5034</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 증명서 발급 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 발급 가능 증명서:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 재학증명서, 졸업증명서, 성적증명서, 수료증명서 등
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 국문/영문 모두 발급 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 온라인 발급:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 정부24(https://www.gov.kr)에서 발급 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 써트피아(https://certpia.com)에서 발급 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🏢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 오프라인 발급:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 대학본부 1층 또는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">미래관 1층 무인발급기 이용
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전과(전공변경), 휴복학, 재입학 등도 학사지원팀에서 처리
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지 참조: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>https://www.hknu.ac.kr/bbs/kor/70/91159/artclView.do?layout=unknown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5037</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🎓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업식 일정
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전기 졸업식: 매년 2월 중순
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 후기 졸업식: 매년 8월 중순
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 정확한 일정은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/92840/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5036</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 등록금 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공 기준의 등록금을 납부하면 됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공을 신청해도 추가 등록금 없음!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 제도 참여 시 별도 장학금 지원은 현재 없음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 등록금 고지, 환불 등은 학교 홈페이지 참조: https://www.hknu.ac.kr/bbs/kor/69/94055/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 재무팀 031-670-5476</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1626,6 +4604,24 @@
       <color theme="1"/>
       <name val="Segoe UI Emoji"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2048,7 +5044,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2068,7 +5064,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2088,7 +5084,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2108,7 +5104,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2128,7 +5124,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2148,7 +5144,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2168,7 +5164,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2188,7 +5184,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2205,7 +5201,7 @@
         <v>34</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -3059,118 +6055,118 @@
       <c r="D58" t="s">
         <v>173</v>
       </c>
-      <c r="F58" t="s">
-        <v>174</v>
+      <c r="F58" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" t="s">
         <v>175</v>
-      </c>
-      <c r="B59" t="s">
-        <v>176</v>
       </c>
       <c r="C59" t="s">
         <v>172</v>
       </c>
       <c r="D59" t="s">
-        <v>177</v>
-      </c>
-      <c r="F59" t="s">
-        <v>178</v>
+        <v>176</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B60" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C60" t="s">
         <v>172</v>
       </c>
       <c r="D60" t="s">
-        <v>181</v>
-      </c>
-      <c r="F60" t="s">
-        <v>182</v>
+        <v>179</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B61" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C61" t="s">
         <v>172</v>
       </c>
       <c r="D61" t="s">
-        <v>185</v>
-      </c>
-      <c r="F61" t="s">
-        <v>186</v>
+        <v>182</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B62" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
         <v>172</v>
       </c>
       <c r="D62" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E62" t="s">
-        <v>190</v>
-      </c>
-      <c r="F62" t="s">
-        <v>191</v>
+        <v>186</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C63" t="s">
         <v>172</v>
       </c>
       <c r="D63" t="s">
-        <v>194</v>
-      </c>
-      <c r="F63" t="s">
-        <v>195</v>
+        <v>189</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B64" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C64" t="s">
         <v>172</v>
       </c>
       <c r="D64" t="s">
-        <v>198</v>
-      </c>
-      <c r="F64" t="s">
-        <v>199</v>
+        <v>192</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B65" t="s">
         <v>120</v>
@@ -3179,18 +6175,18 @@
         <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E65" t="s">
         <v>49</v>
       </c>
       <c r="F65" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B66" t="s">
         <v>120</v>
@@ -3199,428 +6195,428 @@
         <v>30</v>
       </c>
       <c r="D66" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E66" t="s">
         <v>49</v>
       </c>
       <c r="F66" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B67" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C67" t="s">
         <v>172</v>
       </c>
       <c r="D67" t="s">
-        <v>208</v>
-      </c>
-      <c r="F67" t="s">
-        <v>209</v>
+        <v>201</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C68" t="s">
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E68" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F68" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B69" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E69" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F69" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B70" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C70" t="s">
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E70" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F70" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B71" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C71" t="s">
         <v>18</v>
       </c>
       <c r="D71" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E71" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B72" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C72" t="s">
         <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E72" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B73" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
       </c>
       <c r="D73" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E73" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F73" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B74" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C74" t="s">
         <v>27</v>
       </c>
       <c r="D74" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E74" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F74" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B75" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C75" t="s">
         <v>30</v>
       </c>
       <c r="D75" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E75" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F75" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B76" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C76" t="s">
         <v>8</v>
       </c>
       <c r="D76" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B77" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C77" t="s">
         <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F77" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B78" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="F78" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B79" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
       </c>
       <c r="D79" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="F79" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B80" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C80" t="s">
         <v>21</v>
       </c>
       <c r="D80" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F80" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B81" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C81" t="s">
         <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F81" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B82" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C82" t="s">
         <v>30</v>
       </c>
       <c r="D82" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F82" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B83" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C83" t="s">
         <v>172</v>
       </c>
       <c r="D83" t="s">
-        <v>256</v>
-      </c>
-      <c r="F83" t="s">
-        <v>257</v>
+        <v>248</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B84" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C84" t="s">
         <v>172</v>
       </c>
       <c r="D84" t="s">
-        <v>260</v>
-      </c>
-      <c r="F84" t="s">
-        <v>261</v>
+        <v>251</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C85" t="s">
         <v>172</v>
       </c>
       <c r="D85" t="s">
-        <v>263</v>
-      </c>
-      <c r="F85" t="s">
-        <v>264</v>
+        <v>253</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B86" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C86" t="s">
         <v>172</v>
       </c>
       <c r="D86" t="s">
-        <v>266</v>
-      </c>
-      <c r="F86" t="s">
-        <v>267</v>
+        <v>255</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B87" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C87" t="s">
         <v>172</v>
       </c>
       <c r="D87" t="s">
-        <v>269</v>
-      </c>
-      <c r="F87" t="s">
-        <v>270</v>
+        <v>257</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B88" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C88" t="s">
         <v>172</v>
       </c>
       <c r="D88" t="s">
+        <v>259</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="F88" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="B89" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C89" t="s">
         <v>172</v>
       </c>
       <c r="D89" t="s">
-        <v>275</v>
-      </c>
-      <c r="F89" t="s">
-        <v>276</v>
+        <v>261</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB95140-047E-4D28-9DA3-3FC75AF0F5F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA54D75-B8A3-4863-AEBF-62E21F1F43DC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3152,6 +3152,1103 @@
         <rFont val="Segoe UI Emoji"/>
         <family val="2"/>
       </rPr>
+      <t>📝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 관련 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 수강신청:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 매 학기 개강 전 수강신청 기간에 수강신청 시스템(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>http://sugang.hknu.ac.kr)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">에서 신청
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 수강신청 정정기간에 과목 변경 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 수강철회:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학기 중 수강철회 기간에 신청 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 재수강과 다름 (재수강은 이전 성적 대체)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적 이의신청:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적 공시 후 정정기간 내 신청
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 성적확인: 학사시스템(https://info.hknu.ac.kr)에서 조회
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지 참조: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>https://www.hknu.ac.kr/bbs/kor/70/91760/artclView.do?layout=unknown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5032</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학점교류 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학점교류란?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 국내외 대학에서 이수한 학점을 본교 학점으로 인정받는 제도
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 종류:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 국내외 대학 학점교류 (협약 대학 간)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 계절학기 (여름/겨울 방학 중 타교 수강)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 유의사항:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 사전에 학점인정 신청 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 이수구분(전필, 전선, 교양 등) 확인 후 신청
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전공 및 학사지원팀 승인 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지 참조: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>https://www.hknu.ac.kr/bbs/kor/70/92201/artclView.do?layout=unknown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5034</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 증명서 발급 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 발급 가능 증명서:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 재학증명서, 졸업증명서, 성적증명서, 수료증명서 등
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 국문/영문 모두 발급 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 온라인 발급:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 정부24(https://www.gov.kr)에서 발급 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 써트피아(https://certpia.com)에서 발급 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🏢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 오프라인 발급:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 대학본부 1층 또는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">미래관 1층 무인발급기 이용
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전과(전공변경), 휴복학, 재입학 등도 학사지원팀에서 처리
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지 참조: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>https://www.hknu.ac.kr/bbs/kor/70/91159/artclView.do?layout=unknown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5037</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🎓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업식 일정
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 전기 졸업식: 매년 2월 중순
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 후기 졸업식: 매년 8월 중순
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 정확한 일정은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/92840/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5036</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 등록금 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 원전공 기준의 등록금을 납부하면 됨
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공을 신청해도 추가 등록금 없음!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 제도 참여 시 별도 장학금 지원은 현재 없음
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 등록금 고지, 환불 등은 학교 홈페이지 참조: https://www.hknu.ac.kr/bbs/kor/69/94055/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 재무팀 031-670-5476</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
       <t>👨‍🏫</t>
     </r>
     <r>
@@ -3424,7 +4521,7 @@
         <rFont val="Calibri"/>
         <family val="3"/>
       </rPr>
-      <t>https://www.hknu.ac.kr/bbs/kor/70/92919/artclView.do?layout=unknown</t>
+      <t>https://www.hknu.ac.kr/bbs/kor/70/90976/artclView.do?layout=unknown</t>
     </r>
     <r>
       <rPr>
@@ -3457,1103 +4554,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 문의: 학사지원팀 031-670-5036</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 수강 관련 안내
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 수강신청:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 매 학기 개강 전 수강신청 기간에 수강신청 시스템(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t>http://sugang.hknu.ac.kr)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">에서 신청
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 수강신청 정정기간에 과목 변경 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 수강철회:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 학기 중 수강철회 기간에 신청 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 재수강과 다름 (재수강은 이전 성적 대체)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 성적 이의신청:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 성적 공시 후 정정기간 내 신청
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 성적확인: 학사시스템(https://info.hknu.ac.kr)에서 조회
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 학사공지 참조: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t>https://www.hknu.ac.kr/bbs/kor/70/91760/artclView.do?layout=unknown</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5032</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 학점교류 안내
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 학점교류란?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 국내외 대학에서 이수한 학점을 본교 학점으로 인정받는 제도
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 종류:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 국내외 대학 학점교류 (협약 대학 간)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 계절학기 (여름/겨울 방학 중 타교 수강)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 유의사항:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 사전에 학점인정 신청 필요
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 이수구분(전필, 전선, 교양 등) 확인 후 신청
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 전공 및 학사지원팀 승인 필요
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 학사공지 참조: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t>https://www.hknu.ac.kr/bbs/kor/70/92201/artclView.do?layout=unknown</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5034</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 증명서 발급 안내
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 발급 가능 증명서:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 재학증명서, 졸업증명서, 성적증명서, 수료증명서 등
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 국문/영문 모두 발급 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 온라인 발급:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 정부24(https://www.gov.kr)에서 발급 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 써트피아(https://certpia.com)에서 발급 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🏢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 오프라인 발급:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 대학본부 1층 또는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">미래관 1층 무인발급기 이용
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 전과(전공변경), 휴복학, 재입학 등도 학사지원팀에서 처리
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 학사공지 참조: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t>https://www.hknu.ac.kr/bbs/kor/70/91159/artclView.do?layout=unknown</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5037</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🎓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 졸업식 일정
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 전기 졸업식: 매년 2월 중순
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 후기 졸업식: 매년 8월 중순
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 정확한 일정은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/92840/artclView.do?layout=unknown
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 학사지원팀 031-670-5036</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 등록금 안내
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 원전공 기준의 등록금을 납부하면 됨
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 다전공을 신청해도 추가 등록금 없음!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 다전공 제도 참여 시 별도 장학금 지원은 현재 없음
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 등록금 고지, 환불 등은 학교 홈페이지 참조: https://www.hknu.ac.kr/bbs/kor/69/94055/artclView.do?layout=unknown
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 재무팀 031-670-5476</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -6056,7 +6056,7 @@
         <v>173</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -6073,7 +6073,7 @@
         <v>176</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -6090,7 +6090,7 @@
         <v>179</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -6107,7 +6107,7 @@
         <v>182</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -6127,7 +6127,7 @@
         <v>186</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -6144,7 +6144,7 @@
         <v>189</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>복수전공자격, 복수전공조건, 복수전공가능, 복수전공누가, 복수전공몇학년, 복수전공필요학점, 복수전공평점, 복수전공GPA, 복수전공신청자격, 복수전공지원자격, 복수전공요건, 복수전공신청할수있나, 복수전공신청가능한가, 복수전공신청할수있는, 복수전공자격있나, 복수전공자격되나, 복수전공자격충족, 복수전공학점요구, 복수전공학점필요, 복수전공최소학점, 복수전공신청요건, 복수전공신청조건은, 복수전공필요한조건, 복수전공제한사항, 복수전공제약, 복수전공불가능한경우, 복수전공학년제한있나, 복수전공평점필요, 복수전공평점기준, 복수전공누구나가능, 복수전공모두가능, 복수전공신청돼, 복수전공돼, 복수전공가능해, 복수전공가능한가, 복수전공할수있나, 복수전공대상, 복수전공1학년, 복수전공편입생, 복수전공편입</t>
+          <t>복수전공자격, 복수전공조건, 복수전공가능, 복수전공누가, 복수전공몇학년, 복수전공필요학점, 복수전공평점, 복수전공GPA, 복수전공신청자격, 복수전공지원자격, 복수전공요건, 복수전공신청할수있나, 복수전공신청가능한가, 복수전공신청할수있는, 복수전공자격있나, 복수전공자격되나, 복수전공자격충족, 복수전공학점요구, 복수전공학점필요, 복수전공최소학점, 복수전공신청요건, 복수전공신청조건은, 복수전공필요한조건, 복수전공제한사항, 복수전공제약, 복수전공불가능한경우, 복수전공학년제한있나, 복수전공평점필요, 복수전공평점기준, 복수전공누구나가능, 복수전공모두가능, 복수전공신청돼, 복수전공돼, 복수전공가능해, 복수전공가능한가, 복수전공할수있나, 복수전공대상, 복수전공1학년, 복수전공편입생, 복수전공편입,신청할수있을까,신청할수있어,신청가능할까,신청가능해,낮은데,학점낮,학점커트,커트라인,전과했는데,전과를했는데,전과후,도신청,또신청,할수있을까,수있을까,있을까,학점이낮,학점부족</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>복수전공차이, 복수전공비교, 복수전공다른점, 복수전공vs, 복수전공뭐가, 복수전공어떤차이, 복수전공어떤, 복수전공차이점, 복수전공비교해줘, 복수전공뭐가다른, 복수전공어떤게나, 복수전공어떤게좋, 복수전공차이가뭐, 복수전공장단점, 복수전공유리한, 복수전공불리한, 복수전공선택하려면, 복수전공고민중, 복수전공어떤걸선택, 복수전공구분, 복수전공구별, 복수전공차이알려줘, 복수전공비교분석, 복수전공비교해서, 복수전공대조</t>
+          <t>복수전공차이, 복수전공비교, 복수전공다른점, 복수전공vs, 복수전공뭐가, 복수전공어떤차이, 복수전공어떤, 복수전공차이점, 복수전공비교해줘, 복수전공뭐가다른, 복수전공어떤게나, 복수전공어떤게좋, 복수전공차이가뭐, 복수전공장단점, 복수전공유리한, 복수전공불리한, 복수전공선택하려면, 복수전공고민중, 복수전공어떤걸선택, 복수전공구분, 복수전공구별, 복수전공차이알려줘, 복수전공비교분석, 복수전공비교해서, 복수전공대조,차이점이뭐,차이가뭐야,큰차이,가장큰차이,차이점,차이,뭐가다른,뭐가달라</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
@@ -4057,6 +4057,106 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>F101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PROGRAM_INFO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>융합전공</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>졸업장,졸업증명서,졸업증명,표기,찍혀,기재,졸업장에,학위기</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>신청기간,신청자격,포기,변경,취소,비교,차이</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>📌 융합전공과 융합부전공 모두 이수 완료 시 졸업증명서에 표기됩니다.
+💡 궁금한 사항은 학사지원팀(031-670-5035)으로 문의해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>F102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PROGRAM_INFO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>부전공</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>졸업논문,졸업시험,졸업종합시험,논문,시험,졸업종합</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>신청기간,신청자격,포기,변경,취소,비교,차이</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>📌 부전공은 졸업종합시험(논문 포함) 대상에 해당하지 않습니다.
+원 전공의 졸업종합시험 합격 요건만 충족하시면 됩니다.
+💡 궁금한 사항은 학사지원팀(031-670-5035)으로 문의해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>F103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PROGRAM_INFO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>졸업늦어,졸업지연,졸업늦,늦어지나,늦어질,초과학기,졸업미뤄,졸업밀려</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>신청기간,신청자격,포기,변경,취소,비교,차이</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>📌 고학년에 복수전공을 시작하거나 이수 학점이 부족한 경우, 졸업이 지연될 수 있습니다. 이 경우 원 전공과 복수전공의 졸업요건을 모두 충족할 때까지 초과학기로 재학하며 이수를 완료할 수 있습니다.
+💡 졸업 지연을 방지하려면 가급적 저학년부터 계획적으로 복수전공 교과목을 이수하시고, 학기별 이수 계획을 지도교수님과 미리 상담하시길 권장합니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>복수전공취소, 복수전공포기, 복수전공포기절차, 복수전공철회, 복수전공그만, 복수전공중단, 복수전공해지, 복수전공포기하고싶, 복수전공포기하려면, 복수전공포기방법, 복수전공취소하려면, 복수전공취소방법, 복수전공취소하고싶, 복수전공그만두고싶, 복수전공중도포기, 복수전공신청취소, 복수전공철회방법, 복수전공철회하려면, 복수전공해지하려면, 복수전공안하고싶, 복수전공그만하고싶, 복수전공중단하려면, 복수전공포기가능, 복수전공취소가능, 복수전공언제까지포기, 복수전공포기기한, 복수전공취소기한, 복수전공취소어떻게, 복수전공포기어떻게, 복수전공철회어떻게</t>
+          <t>복수전공취소, 복수전공포기, 복수전공포기절차, 복수전공철회, 복수전공그만, 복수전공중단, 복수전공해지, 복수전공포기하고싶, 복수전공포기하려면, 복수전공포기방법, 복수전공취소하려면, 복수전공취소방법, 복수전공취소하고싶, 복수전공그만두고싶, 복수전공중도포기, 복수전공신청취소, 복수전공철회방법, 복수전공철회하려면, 복수전공해지하려면, 복수전공안하고싶, 복수전공그만하고싶, 복수전공중단하려면, 복수전공포기가능, 복수전공취소가능, 복수전공언제까지포기, 복수전공포기기한, 복수전공취소기한, 복수전공취소어떻게, 복수전공포기어떻게, 복수전공철회어떻게,마음바뀌면,취소할수,취소가능,취소할수있어,취소하고싶,취소하려면,나중에취소</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>복수전공학점, 복수전공몇학점, 복수전공이수, 복수전공이수학점, 복수전공필수학점, 복수전공졸업학점, 복수전공총학점, 복수전공필요학점, 복수전공이수해야할학점, 복수전공학점체계, 복수전공학점구조, 복수전공학점계산, 복수전공몇학점필요, 복수전공몇학점들어야, 복수전공학점기준, 복수전공최소학점, 복수전공필수이수, 복수전공이수학점은, 복수전공학점충족, 복수전공학점조건, 복수전공졸업요건학점, 복수전공인정학점, 복수전공이수학점확인</t>
+          <t>복수전공학점, 복수전공몇학점, 복수전공이수, 복수전공이수학점, 복수전공필수학점, 복수전공졸업학점, 복수전공총학점, 복수전공필요학점, 복수전공이수해야할학점, 복수전공학점체계, 복수전공학점구조, 복수전공학점계산, 복수전공몇학점필요, 복수전공몇학점들어야, 복수전공학점기준, 복수전공최소학점, 복수전공필수이수, 복수전공이수학점은, 복수전공학점충족, 복수전공학점조건, 복수전공졸업요건학점, 복수전공인정학점, 복수전공이수학점확인,최소이수학점,최소학점,몇학점이야,몇학점이수,이수학점이몇,학점이몇,몇학점</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>부전공학점, 부전공몇학점, 부전공이수, 부전공이수학점, 부전공필수학점, 부전공졸업학점, 부전공총학점, 부전공필요학점, 부전공이수해야할학점, 부전공학점체계, 부전공학점구조, 부전공학점계산, 부전공몇학점필요, 부전공몇학점들어야, 부전공학점기준, 부전공최소학점, 부전공필수이수, 부전공이수학점은, 부전공학점충족, 부전공학점조건, 부전공졸업요건학점, 부전공인정학점, 부전공이수학점확인</t>
+          <t>부전공학점, 부전공몇학점, 부전공이수, 부전공이수학점, 부전공필수학점, 부전공졸업학점, 부전공총학점, 부전공필요학점, 부전공이수해야할학점, 부전공학점체계, 부전공학점구조, 부전공학점계산, 부전공몇학점필요, 부전공몇학점들어야, 부전공학점기준, 부전공최소학점, 부전공필수이수, 부전공이수학점은, 부전공학점충족, 부전공학점조건, 부전공졸업요건학점, 부전공인정학점, 부전공이수학점확인,최소이수학점,최소학점,몇학점이야,몇학점이수,이수학점이몇,학점이몇,몇학점</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2578,6 +2578,11 @@
       <c r="D59" t="inlineStr">
         <is>
           <t>졸업식, 졸업식은, 졸업식은언제, 학위수여식은, 학위수여식은언제, 졸업, 학위수여, 졸업일정, 졸업날짜, 졸업시기, 학위받는날, 언제졸업, 졸업하는날</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>성적이나빠,성적나빠,영향이없어,영향없어,영향,재수강</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4157,6 +4162,467 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>F104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CONCURRENT_ENROLL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>다전공</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>동시에신청,동시신청,중복신청,중복이수,같이신청,함께신청,두개신청,두개동시,복수전공부전공동시,부전공복수전공동시</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>⚠️ 소단위전공과정(마이크로디그리)을 제외하고 다전공은 중복 이수가 불가합니다.
+예를 들어 복수전공과 부전공, 복수전공과 연계전공 등을 동시에 신청하는 것은 허용되지 않습니다.
+✅ 마이크로디그리는 제한 없이 여러 개 이수 가능!</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>F105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>APPLY_METHOD</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>연계전공</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>연계전공신청방법,연계전공어떻게신청,연계전공신청방식,연계전공방법,연계전공어떻게,어떻게신청,신청방법,신청방식,방법이달라,방법달라</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>기간,언제,마감</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>📋 연계전공 신청 방법과 시기는 복수전공과 유사하며, 매 학기 학사공지를 통해 안내됩니다.
+연계전공은 관련 전공의 교과목을 9학점 이상 이수하는 방식으로 운영됩니다.
+💡 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>F106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PROGRAM_INFO</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>융합전공</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>융합전공만들,융합전공고르,융합전공선택,융합전공정해진,정해진것중,원하는걸만들,고르는거,선택하는거</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>신청기간,신청자격,포기,변경,취소,비교,차이</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>📌 융합전공은 대학에서 미리 설계·개설한 전공 중에서 선택하는 방식입니다. 학생이 직접 교육과정을 설계하는 학생설계전공과는 다릅니다.
+💡 현재 개설된 융합전공 목록은 사이드 메뉴의 '다전공 제도 안내'에서 확인하실 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>F107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CREDIT_INFO</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>복수전공최소,복수전공최소이수,복수전공최소학점,복수전공몇학점이야,복수전공학점이몇</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>신청기간,신청자격,포기,변경,취소,비교,차이,한학기최대,최대학점,학기당</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>📊 복수전공은 해당 전공의 전공필수를 포함하여 39학점 이상을 이수해야 합니다.
+▸ 인문사회계열(법학전공 제외)은 36학점 이상
+💡 더 자세한 사항은 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>F108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CREDIT_INFO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>부전공</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>부전공최소,부전공최소이수,부전공최소학점,부전공몇학점이야,부전공학점이몇</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>신청기간,신청자격,포기,변경,취소,비교,차이</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>📊 부전공은 해당 전공의 전공필수를 포함하여 27학점 이상을 이수해야 합니다.
+💡 더 자세한 사항은 왼쪽 사이드바의 '다전공 제도 안내' 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>F109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>APPLY_QUALIFICATION</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>편입학생,편입생,편입,편입학생복수전공,편입생복수전공,편입학생신청,편입생신청</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>✅ 편입학생도 재학 중 복수전공 신청이 가능합니다.
+💡 신청 시기와 방법 등은 학사공지를 참고해 주세요: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>F110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PROGRAM_TUITION</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>복수전공등록금,등록금더,추가등록금,등록금추가,등록금나와,등록금부담,복수전공비용,복수전공돈,등록금이더,등록금더나,등록금나,추가등록,등록금추가로</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>💰 복수전공 이수로 인해 별도의 추가 등록금이 부과되지는 않습니다.
+▸ 다만, 졸업 지연으로 인해 초과학기가 발생하는 경우 초과 학기에 대한 등록금은 납부해야 합니다.
+💡 등록금 관련 문의: 재무팀 031-670-5476</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>F111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PROGRAM_INFO</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>장학금불이익,장학금신청,복수전공장학금,장학금영향,장학금불이익,복수전공하면장학금</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>📌 복수전공 이수 자체가 장학금 신청에 불이익을 주지는 않습니다.
+다만, 장학금 종류에 따라 이수 학점, 평점 기준 등 수혜 조건이 다를 수 있으므로, 본인이 신청하려는 장학금의 요건을 장학 담당 부서에 확인하시기 바랍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>F112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>APPLY_QUALIFICATION</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>휴학중신청,휴학기간신청,휴학중복수전공,휴학기간중,휴학중에도,휴학중에신청,휴학상태에서,휴학중에도신청,휴학중에복수전공,휴학기간복수전공,휴학중복수,휴학신청,휴학중다전공</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>📌 다전공 신청 자체는 휴학 중에도 가능할 수 있으나, 실제 이수(수업 수강)는 해당 학기에 반드시 복학한 상태여야 합니다.
+💡 정확한 신청 가능 여부는 학사지원팀(031-670-5035)에 확인하시기 바랍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>F113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PROGRAM_INFO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>부전공</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>부전공졸업증명서,부전공표기,부전공졸업증명,부전공졸업장,부전공기재,부전공어떻게표기,졸업증명서에,졸업증명서표기,어떻게표기,표기돼,표기되,증명서에표기</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>신청기간,신청자격,포기,변경,취소,비교,차이</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>📌 부전공을 이수 완료한 경우 졸업증명서에 부전공 이수 사실이 표기됩니다.
+이수 중인 상태에서는 표기되지 않으며, 졸업 시점에 최종 확정됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>F114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>APPLY_CANCEL</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>다전공</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>포기하면학점,중간에포기,포기하면과목,포기후학점,포기시학점,포기했을때,들은과목학점,이수한학점</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>📌 다전공 신청을 취소하더라도 이미 이수한 교과목의 학점은 취소되지 않으며, 해당 학점은 원 전공의 자유선택 학점으로 인정됩니다.
+전체 평점평균과 졸업 학점에도 그대로 반영됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>F115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PROGRAM_INFO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>자격증,자격증취득,자격증도움,자격증관련,자격증연계,도움이되는,도움되는,자격증도움이,자격증에도움</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>비교,차이,신청기간,포기</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>💡 자격증과 연계성이 높은 전공은 목표 자격증의 응시 요건 및 관련 전공과 연결하여 선택하는 것이 효과적입니다.
+구체적인 추천은 해당 전공 사무실에 문의하시기 바랍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>F116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PROGRAM_INFO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>이직,직무변경,직무전환,이직도움,취업후,전환도움</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>비교,차이,신청기간,포기,채용,부전공인정</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>📌 복수전공 이수는 새로운 분야로의 직무 전환이나 이직 시 관련 역량을 갖추고 있음을 증명하는 데 도움이 될 수 있습니다.
+다만, 실무 경험이나 자격증과 함께 준비하는 것이 더욱 효과적입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>F117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>APPLY_PERIOD</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>다전공</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>매학기신청,특정시기,신청시기,아무때나,수시로,항상신청,아무때나신청,제도신청</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>📅 다전공 신청은 학기별로 정해진 기간에만 가능합니다.
+신청 기간은 매 학기초, 학기말(2회) 학사공지를 통해 안내되므로, 홈페이지 공지사항을 확인하시기 바랍니다.
+💡 학사공지: https://www.hknu.ac.kr/bbs/kor/70/94454/artclView.do?layout=unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>F118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>APPLY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>복수전공</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>원전공바꾸,원전공변경,전과복수전공,전과하면복수전공,원전공을바꾸,복수전공중전과,전과신청복수전공,바꾸고싶,바꾸고싶으면,변경하고싶,전공바꾸</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>📌 전과(원 전공 변경)와 복수전공은 별개의 제도입니다.
+전과 신청 시 기존 복수전공 이수 현황이 어떻게 처리되는지는 경우에 따라 달라질 수 있습니다.
+💡 궁금한 사항은 학사지원팀(031-670-5035)으로 문의해 주세요.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>

--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -2652,7 +2652,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>학점교류, 학점인정, 타대학, 타교, 다른학교, 학점인정방법, 학점인정되나, 인정받나, 교환학생, 교류학점, 타교학점</t>
+          <t>학점교류, 학점인정, 타대학, 타교, 다른학교, 학점인정방법, 학점인정되나, 인정받나, 교환학생, 교류학점, 타교학점,계절학기,계절학기신청,계절학기방법</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
